--- a/R/data/quiz_250317.xlsx
+++ b/R/data/quiz_250317.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="244">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -476,6 +476,273 @@
   </si>
   <si>
     <t>황지영</t>
+  </si>
+  <si>
+    <t>yenny0302@naver.com</t>
+  </si>
+  <si>
+    <t>간호</t>
+  </si>
+  <si>
+    <t>양예빈</t>
+  </si>
+  <si>
+    <t>loverin12@naver.com</t>
+  </si>
+  <si>
+    <t>임혜린</t>
+  </si>
+  <si>
+    <t>dahyeon057@naver.com</t>
+  </si>
+  <si>
+    <t>경제학과</t>
+  </si>
+  <si>
+    <t>한다현</t>
+  </si>
+  <si>
+    <t>limsa3173@gmail.com</t>
+  </si>
+  <si>
+    <t>임승언</t>
+  </si>
+  <si>
+    <t>wjdrjs0111@gmail.com</t>
+  </si>
+  <si>
+    <t>정건</t>
+  </si>
+  <si>
+    <t>parksungwon0718@gmail.com</t>
+  </si>
+  <si>
+    <t>화학과</t>
+  </si>
+  <si>
+    <t>박성원</t>
+  </si>
+  <si>
+    <t>binkim112@gmail.com</t>
+  </si>
+  <si>
+    <t>김종빈</t>
+  </si>
+  <si>
+    <t>050306kdy@gmail.com</t>
+  </si>
+  <si>
+    <t>미래융합스쿨 의약신소재학과</t>
+  </si>
+  <si>
+    <t>김도영</t>
+  </si>
+  <si>
+    <t>bin9720@naver.com</t>
+  </si>
+  <si>
+    <t>미래융합스쿨</t>
+  </si>
+  <si>
+    <t>박채빈</t>
+  </si>
+  <si>
+    <t>jaena0830@naver.com</t>
+  </si>
+  <si>
+    <t>언어병리학과</t>
+  </si>
+  <si>
+    <t>양재나</t>
+  </si>
+  <si>
+    <t>caj1020@naver.com</t>
+  </si>
+  <si>
+    <t>채아진</t>
+  </si>
+  <si>
+    <t>lgn0915@naver.com</t>
+  </si>
+  <si>
+    <t>청각학과</t>
+  </si>
+  <si>
+    <t>임지인</t>
+  </si>
+  <si>
+    <t>kseoj123@naver.com</t>
+  </si>
+  <si>
+    <t>김서진</t>
+  </si>
+  <si>
+    <t>dongil00001@naver.com</t>
+  </si>
+  <si>
+    <t>김동일</t>
+  </si>
+  <si>
+    <t>jihyunkim917@gmail.com</t>
+  </si>
+  <si>
+    <t>인문학부</t>
+  </si>
+  <si>
+    <t>김지현</t>
+  </si>
+  <si>
+    <t>yongjun8844@gmail.com</t>
+  </si>
+  <si>
+    <t>소프트웨어융합(빅데이터)</t>
+  </si>
+  <si>
+    <t>안용준</t>
+  </si>
+  <si>
+    <t>hschang0924@gmail.com</t>
+  </si>
+  <si>
+    <t>장현수</t>
+  </si>
+  <si>
+    <t>sarahmood@naver.com</t>
+  </si>
+  <si>
+    <t>복은비</t>
+  </si>
+  <si>
+    <t>donghun2477@naver.com</t>
+  </si>
+  <si>
+    <t>법학과</t>
+  </si>
+  <si>
+    <t>한동훈</t>
+  </si>
+  <si>
+    <t>lswon916@naver.com</t>
+  </si>
+  <si>
+    <t>이서원</t>
+  </si>
+  <si>
+    <t>wshs_ws@naver.com</t>
+  </si>
+  <si>
+    <t>소프트웨어학부 컨텐츠IT</t>
+  </si>
+  <si>
+    <t>이우성</t>
+  </si>
+  <si>
+    <t>a01063579093@gmail.com</t>
+  </si>
+  <si>
+    <t>권민정</t>
+  </si>
+  <si>
+    <t>deoduck877@naver.com</t>
+  </si>
+  <si>
+    <t>김동규</t>
+  </si>
+  <si>
+    <t>kimdw9510@gmail.com</t>
+  </si>
+  <si>
+    <t>김동우</t>
+  </si>
+  <si>
+    <t>choiy617@naver.com</t>
+  </si>
+  <si>
+    <t>철학과</t>
+  </si>
+  <si>
+    <t>최원찬</t>
+  </si>
+  <si>
+    <t>dhdhdh1010@naver.com</t>
+  </si>
+  <si>
+    <t>김도희</t>
+  </si>
+  <si>
+    <t>minbh5642@gmail.com</t>
+  </si>
+  <si>
+    <t>민병현</t>
+  </si>
+  <si>
+    <t>yyeon0245@gmail.com</t>
+  </si>
+  <si>
+    <t>디지털미디어콘텐츠전공</t>
+  </si>
+  <si>
+    <t>김연우</t>
+  </si>
+  <si>
+    <t>ttendragoon666@gmail.com</t>
+  </si>
+  <si>
+    <t>이용우</t>
+  </si>
+  <si>
+    <t>yoonchw901@naver.com</t>
+  </si>
+  <si>
+    <t>윤초원</t>
+  </si>
+  <si>
+    <t>parkchaebin7890@gmail.com</t>
+  </si>
+  <si>
+    <t>디지털미디어콘텐츠 전공</t>
+  </si>
+  <si>
+    <t>csb5042@hanmail.net</t>
+  </si>
+  <si>
+    <t>최수빈</t>
+  </si>
+  <si>
+    <t>tjwldus5810@naver.com</t>
+  </si>
+  <si>
+    <t>서지연</t>
+  </si>
+  <si>
+    <t>sol3499@naver.com</t>
+  </si>
+  <si>
+    <t>미래융합스쿨 융합신소재 전공</t>
+  </si>
+  <si>
+    <t>주찬솔</t>
+  </si>
+  <si>
+    <t>retmiof32145@gmail.com</t>
+  </si>
+  <si>
+    <t>미디어스쿨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">권지욱 </t>
+  </si>
+  <si>
+    <t>jyk3642@naver.com</t>
+  </si>
+  <si>
+    <t>김정연</t>
+  </si>
+  <si>
+    <t>wkdguswns16@naver.com</t>
+  </si>
+  <si>
+    <t>장현준</t>
   </si>
 </sst>
 </file>
@@ -506,7 +773,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -639,10 +906,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -650,27 +917,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -680,7 +933,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -792,9 +1045,6 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -853,7 +1103,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N44" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N81" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -2869,44 +3119,1561 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="32">
+      <c r="A44" s="20">
         <v>45733.919978148144</v>
       </c>
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="C44" s="33" t="s">
+      <c r="C44" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="21">
         <v>2.0211637E7</v>
       </c>
-      <c r="E44" s="33" t="s">
+      <c r="E44" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="F44" s="34" t="s">
+      <c r="F44" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="G44" s="35">
-        <v>0.2</v>
-      </c>
-      <c r="H44" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="I44" s="33" t="s">
+      <c r="G44" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H44" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I44" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="J44" s="36">
-        <v>0.059</v>
-      </c>
-      <c r="K44" s="33" t="s">
+      <c r="J44" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K44" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="L44" s="33" t="s">
+      <c r="L44" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="N44" s="37" t="s">
+      <c r="N44" s="25" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="26">
+        <v>45733.93991380787</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" s="27">
+        <v>2.0246255E7</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H45" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I45" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J45" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K45" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L45" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M45" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20">
+        <v>45733.96216871528</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" s="21">
+        <v>2.0241533E7</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H46" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I46" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J46" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K46" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N46" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26">
+        <v>45733.96514482639</v>
+      </c>
+      <c r="B47" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C47" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="D47" s="27">
+        <v>2.0242853E7</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G47" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H47" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I47" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J47" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K47" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L47" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N47" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20">
+        <v>45733.97601168981</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="21">
+        <v>2.0226281E7</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H48" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I48" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J48" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K48" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N48" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26">
+        <v>45734.37158400463</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49" s="27">
+        <v>2.0244142E7</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="F49" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G49" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H49" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I49" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J49" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K49" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M49" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20">
+        <v>45734.37704959491</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D50" s="21">
+        <v>2.024341E7</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G50" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="H50" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I50" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J50" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K50" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L50" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N50" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="26">
+        <v>45734.419992372685</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="27">
+        <v>2.024211E7</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H51" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I51" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J51" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K51" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L51" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N51" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20">
+        <v>45734.44866648148</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D52" s="21">
+        <v>2.0246609E7</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="F52" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H52" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I52" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J52" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K52" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L52" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N52" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="26">
+        <v>45734.4492746412</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="D53" s="27">
+        <v>2.0246625E7</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G53" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H53" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I53" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J53" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K53" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L53" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M53" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20">
+        <v>45734.46765853009</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" s="21">
+        <v>2.0243925E7</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H54" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I54" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J54" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K54" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L54" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N54" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="26">
+        <v>45734.46774439815</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C55" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="D55" s="27">
+        <v>2.0243958E7</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G55" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H55" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I55" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J55" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K55" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L55" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N55" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20">
+        <v>45734.467777638885</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" s="21">
+        <v>2.0243944E7</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="F56" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H56" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I56" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J56" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K56" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L56" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N56" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="26">
+        <v>45734.46782023148</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="D57" s="27">
+        <v>2.0243906E7</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="F57" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G57" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H57" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I57" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K57" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M57" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20">
+        <v>45734.47408994213</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D58" s="21">
+        <v>2.0232408E7</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="F58" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G58" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H58" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I58" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J58" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K58" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L58" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M58" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="26">
+        <v>45734.51374202546</v>
+      </c>
+      <c r="B59" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" s="27">
+        <v>2.0241024E7</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="F59" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H59" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J59" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K59" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L59" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N59" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20">
+        <v>45734.51949900463</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D60" s="21">
+        <v>2.0225188E7</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="F60" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G60" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H60" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I60" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J60" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K60" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L60" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N60" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="26">
+        <v>45734.56658530093</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D61" s="27">
+        <v>2.0242431E7</v>
+      </c>
+      <c r="E61" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F61" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G61" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="H61" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I61" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J61" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K61" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L61" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M61" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20">
+        <v>45734.5875340162</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D62" s="21">
+        <v>2.0222823E7</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="F62" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G62" s="23">
+        <v>0.25</v>
+      </c>
+      <c r="H62" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I62" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J62" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K62" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L62" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N62" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="26">
+        <v>45734.60268855324</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="C63" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D63" s="27">
+        <v>2.0222761E7</v>
+      </c>
+      <c r="E63" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="F63" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="29">
+        <v>0.25</v>
+      </c>
+      <c r="H63" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I63" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J63" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K63" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L63" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M63" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20">
+        <v>45734.633527314814</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D64" s="21">
+        <v>2.0243936E7</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="F64" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G64" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H64" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I64" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K64" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="L64" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M64" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="26">
+        <v>45734.636382662036</v>
+      </c>
+      <c r="B65" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="C65" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="D65" s="27">
+        <v>2.0237104E7</v>
+      </c>
+      <c r="E65" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="F65" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G65" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H65" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I65" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" s="30">
+        <v>0.374</v>
+      </c>
+      <c r="K65" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L65" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M65" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20">
+        <v>45734.65744732639</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" s="21">
+        <v>2.0241506E7</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="F66" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G66" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H66" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I66" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J66" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K66" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L66" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N66" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="26">
+        <v>45734.66083583333</v>
+      </c>
+      <c r="B67" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="C67" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D67" s="27">
+        <v>2.0195122E7</v>
+      </c>
+      <c r="E67" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="F67" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G67" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H67" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I67" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J67" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K67" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M67" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="20">
+        <v>45734.66499668981</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D68" s="21">
+        <v>2.0242807E7</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="F68" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H68" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I68" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K68" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L68" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N68" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="26">
+        <v>45734.68943290509</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="C69" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="D69" s="27">
+        <v>2.0231097E7</v>
+      </c>
+      <c r="E69" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="F69" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G69" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H69" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I69" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="30">
+        <v>0.374</v>
+      </c>
+      <c r="K69" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L69" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M69" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20">
+        <v>45734.7026084838</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D70" s="21">
+        <v>2.0242208E7</v>
+      </c>
+      <c r="E70" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="F70" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G70" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="H70" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I70" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J70" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K70" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L70" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N70" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="26">
+        <v>45734.72174729167</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="C71" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="D71" s="27">
+        <v>2.0251036E7</v>
+      </c>
+      <c r="E71" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="F71" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G71" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="H71" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I71" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J71" s="30">
+        <v>0.002</v>
+      </c>
+      <c r="K71" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L71" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N71" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="20">
+        <v>45734.74581331019</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="D72" s="21">
+        <v>2.0232517E7</v>
+      </c>
+      <c r="E72" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="F72" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G72" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H72" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I72" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J72" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K72" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L72" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N72" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="26">
+        <v>45734.777097638886</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C73" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D73" s="27">
+        <v>2.022163E7</v>
+      </c>
+      <c r="E73" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="F73" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G73" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H73" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I73" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" s="30">
+        <v>0.374</v>
+      </c>
+      <c r="K73" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L73" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M73" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="20">
+        <v>45734.848556412035</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74" s="21">
+        <v>2.0242993E7</v>
+      </c>
+      <c r="E74" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="F74" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G74" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H74" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I74" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J74" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K74" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L74" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N74" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="26">
+        <v>45734.86953831019</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C75" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="D75" s="27">
+        <v>2.0242524E7</v>
+      </c>
+      <c r="E75" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="F75" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G75" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H75" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I75" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J75" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K75" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L75" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N75" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20">
+        <v>45734.87342363426</v>
+      </c>
+      <c r="B76" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D76" s="21">
+        <v>2.0242849E7</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="F76" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G76" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H76" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I76" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J76" s="24">
+        <v>0.374</v>
+      </c>
+      <c r="K76" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L76" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N76" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="26">
+        <v>45734.87389268518</v>
+      </c>
+      <c r="B77" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C77" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D77" s="27">
+        <v>2.0242328E7</v>
+      </c>
+      <c r="E77" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="F77" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G77" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H77" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I77" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J77" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K77" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L77" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N77" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20">
+        <v>45734.87437498843</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="D78" s="21">
+        <v>2.0216641E7</v>
+      </c>
+      <c r="E78" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="F78" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G78" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H78" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K78" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L78" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N78" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="26">
+        <v>45734.883153229166</v>
+      </c>
+      <c r="B79" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="C79" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="D79" s="27">
+        <v>2.0242505E7</v>
+      </c>
+      <c r="E79" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="F79" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G79" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H79" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I79" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J79" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K79" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L79" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N79" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20">
+        <v>45734.88817575232</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D80" s="21">
+        <v>2.022708E7</v>
+      </c>
+      <c r="E80" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="F80" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G80" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H80" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I80" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J80" s="24">
+        <v>0.374</v>
+      </c>
+      <c r="K80" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L80" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M80" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="32">
+        <v>45734.892779525464</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="C81" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="D81" s="33">
+        <v>2.0213033E7</v>
+      </c>
+      <c r="E81" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="F81" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="G81" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="H81" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I81" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J81" s="36">
+        <v>0.059</v>
+      </c>
+      <c r="K81" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="L81" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="M81" s="33" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250317.xlsx
+++ b/R/data/quiz_250317.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2966" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3182" uniqueCount="839">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2375,6 +2375,159 @@
   </si>
   <si>
     <t>정민서</t>
+  </si>
+  <si>
+    <t>cny120333@naver.com</t>
+  </si>
+  <si>
+    <t>디지털인문예술</t>
+  </si>
+  <si>
+    <t>최나연</t>
+  </si>
+  <si>
+    <t>ngjh1026@gmail.com</t>
+  </si>
+  <si>
+    <t>남궁정현</t>
+  </si>
+  <si>
+    <t>yourim1207@naver.com</t>
+  </si>
+  <si>
+    <t>오유림</t>
+  </si>
+  <si>
+    <t>namu6186@naver.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">김남우 </t>
+  </si>
+  <si>
+    <t>mins4092@naver.com</t>
+  </si>
+  <si>
+    <t>AI기술경영융합</t>
+  </si>
+  <si>
+    <t>김민성</t>
+  </si>
+  <si>
+    <t>juheepoiu@gmail.com</t>
+  </si>
+  <si>
+    <t>임주희</t>
+  </si>
+  <si>
+    <t>hongbeens@gmail.com</t>
+  </si>
+  <si>
+    <t>조홍빈</t>
+  </si>
+  <si>
+    <t>hanhh3209@naver.com</t>
+  </si>
+  <si>
+    <t>한혜민</t>
+  </si>
+  <si>
+    <t>lamsys@naver.com</t>
+  </si>
+  <si>
+    <t>정시효</t>
+  </si>
+  <si>
+    <t>uksongcheol@naver.com</t>
+  </si>
+  <si>
+    <t>김성철</t>
+  </si>
+  <si>
+    <t>mhk02083@naver.com</t>
+  </si>
+  <si>
+    <t>명희경</t>
+  </si>
+  <si>
+    <t>0812hhh37@gmail.com</t>
+  </si>
+  <si>
+    <t>최아영</t>
+  </si>
+  <si>
+    <t>cksgh582@gmail.com</t>
+  </si>
+  <si>
+    <t>박찬호</t>
+  </si>
+  <si>
+    <t>bong8hee@gmail.com</t>
+  </si>
+  <si>
+    <t>강태웅</t>
+  </si>
+  <si>
+    <t>kwan0172@gmail.com</t>
+  </si>
+  <si>
+    <t>김관형</t>
+  </si>
+  <si>
+    <t>kangsmooth@naver.com</t>
+  </si>
+  <si>
+    <t>강령현</t>
+  </si>
+  <si>
+    <t>jung5jung59708@gmail.com</t>
+  </si>
+  <si>
+    <t>정서현</t>
+  </si>
+  <si>
+    <t>rms2004gml@naver.com</t>
+  </si>
+  <si>
+    <t>장근희</t>
+  </si>
+  <si>
+    <t>ychoe119@gmail.com</t>
+  </si>
+  <si>
+    <t>최윤서</t>
+  </si>
+  <si>
+    <t>qmpzalwn@naver.com</t>
+  </si>
+  <si>
+    <t>오유택</t>
+  </si>
+  <si>
+    <t>yugyuhyeon023@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">자연과학대학 자율전공 </t>
+  </si>
+  <si>
+    <t>유규현</t>
+  </si>
+  <si>
+    <t>seunggu4500@gmail.com</t>
+  </si>
+  <si>
+    <t>김승구</t>
+  </si>
+  <si>
+    <t>iamhdm@naver.com</t>
+  </si>
+  <si>
+    <t>황동민</t>
+  </si>
+  <si>
+    <t>renatta@naver.com</t>
+  </si>
+  <si>
+    <t>이예원</t>
   </si>
 </sst>
 </file>
@@ -2405,7 +2558,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -2561,25 +2714,11 @@
         <color rgb="FF442F65"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2691,9 +2830,6 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2752,7 +2888,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N329" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N353" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -16453,44 +16589,1028 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="32">
+      <c r="A329" s="26">
         <v>45739.98251740741</v>
       </c>
-      <c r="B329" s="33" t="s">
+      <c r="B329" s="27" t="s">
         <v>786</v>
       </c>
-      <c r="C329" s="33" t="s">
+      <c r="C329" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="D329" s="33">
+      <c r="D329" s="27">
         <v>2.0256637E7</v>
       </c>
-      <c r="E329" s="33" t="s">
+      <c r="E329" s="27" t="s">
         <v>787</v>
       </c>
-      <c r="F329" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="G329" s="35">
-        <v>0.2</v>
-      </c>
-      <c r="H329" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="I329" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J329" s="36">
-        <v>0.059</v>
-      </c>
-      <c r="K329" s="33" t="s">
+      <c r="F329" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G329" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H329" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I329" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J329" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K329" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="L329" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="N329" s="37" t="s">
-        <v>28</v>
+      <c r="L329" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N329" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="20">
+        <v>45740.4044116088</v>
+      </c>
+      <c r="B330" s="21" t="s">
+        <v>788</v>
+      </c>
+      <c r="C330" s="21" t="s">
+        <v>789</v>
+      </c>
+      <c r="D330" s="21">
+        <v>2.0236637E7</v>
+      </c>
+      <c r="E330" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="F330" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G330" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H330" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I330" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J330" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K330" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L330" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M330" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="26">
+        <v>45740.57603630787</v>
+      </c>
+      <c r="B331" s="27" t="s">
+        <v>791</v>
+      </c>
+      <c r="C331" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="D331" s="27">
+        <v>2.0232813E7</v>
+      </c>
+      <c r="E331" s="27" t="s">
+        <v>792</v>
+      </c>
+      <c r="F331" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G331" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="H331" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I331" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J331" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K331" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="L331" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M331" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="20">
+        <v>45740.578852164355</v>
+      </c>
+      <c r="B332" s="21" t="s">
+        <v>793</v>
+      </c>
+      <c r="C332" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D332" s="21">
+        <v>2.0242223E7</v>
+      </c>
+      <c r="E332" s="21" t="s">
+        <v>794</v>
+      </c>
+      <c r="F332" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G332" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H332" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I332" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J332" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K332" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L332" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N332" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="26">
+        <v>45740.64343376158</v>
+      </c>
+      <c r="B333" s="27" t="s">
+        <v>795</v>
+      </c>
+      <c r="C333" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D333" s="27">
+        <v>2.0221506E7</v>
+      </c>
+      <c r="E333" s="27" t="s">
+        <v>796</v>
+      </c>
+      <c r="F333" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G333" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H333" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I333" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J333" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K333" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L333" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M333" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="20">
+        <v>45740.64585444445</v>
+      </c>
+      <c r="B334" s="21" t="s">
+        <v>797</v>
+      </c>
+      <c r="C334" s="21" t="s">
+        <v>798</v>
+      </c>
+      <c r="D334" s="21">
+        <v>2.0226711E7</v>
+      </c>
+      <c r="E334" s="21" t="s">
+        <v>799</v>
+      </c>
+      <c r="F334" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G334" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H334" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I334" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J334" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K334" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L334" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N334" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="26">
+        <v>45740.663272418984</v>
+      </c>
+      <c r="B335" s="27" t="s">
+        <v>800</v>
+      </c>
+      <c r="C335" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="D335" s="27">
+        <v>2.024108E7</v>
+      </c>
+      <c r="E335" s="27" t="s">
+        <v>801</v>
+      </c>
+      <c r="F335" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G335" s="29">
+        <v>0.25</v>
+      </c>
+      <c r="H335" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I335" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J335" s="30">
+        <v>0.002</v>
+      </c>
+      <c r="K335" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="L335" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N335" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="20">
+        <v>45740.67314050926</v>
+      </c>
+      <c r="B336" s="21" t="s">
+        <v>802</v>
+      </c>
+      <c r="C336" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D336" s="21">
+        <v>2.0243255E7</v>
+      </c>
+      <c r="E336" s="21" t="s">
+        <v>803</v>
+      </c>
+      <c r="F336" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G336" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H336" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I336" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J336" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K336" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="L336" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M336" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="26">
+        <v>45740.67573560185</v>
+      </c>
+      <c r="B337" s="27" t="s">
+        <v>804</v>
+      </c>
+      <c r="C337" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D337" s="27">
+        <v>2.0242759E7</v>
+      </c>
+      <c r="E337" s="27" t="s">
+        <v>805</v>
+      </c>
+      <c r="F337" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G337" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="H337" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I337" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J337" s="30">
+        <v>0.002</v>
+      </c>
+      <c r="K337" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L337" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N337" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="20">
+        <v>45740.715410115736</v>
+      </c>
+      <c r="B338" s="21" t="s">
+        <v>806</v>
+      </c>
+      <c r="C338" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D338" s="21">
+        <v>2.0243427E7</v>
+      </c>
+      <c r="E338" s="21" t="s">
+        <v>807</v>
+      </c>
+      <c r="F338" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G338" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H338" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I338" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J338" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K338" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L338" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M338" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="26">
+        <v>45740.73196488426</v>
+      </c>
+      <c r="B339" s="27" t="s">
+        <v>808</v>
+      </c>
+      <c r="C339" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D339" s="27">
+        <v>2.0192204E7</v>
+      </c>
+      <c r="E339" s="27" t="s">
+        <v>809</v>
+      </c>
+      <c r="F339" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G339" s="29">
+        <v>0.25</v>
+      </c>
+      <c r="H339" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I339" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J339" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K339" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L339" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M339" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="20">
+        <v>45740.73942513889</v>
+      </c>
+      <c r="B340" s="21" t="s">
+        <v>810</v>
+      </c>
+      <c r="C340" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D340" s="21">
+        <v>2.0232613E7</v>
+      </c>
+      <c r="E340" s="21" t="s">
+        <v>811</v>
+      </c>
+      <c r="F340" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G340" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H340" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I340" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J340" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K340" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L340" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M340" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="26">
+        <v>45740.77524854167</v>
+      </c>
+      <c r="B341" s="27" t="s">
+        <v>812</v>
+      </c>
+      <c r="C341" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D341" s="27">
+        <v>2.0243047E7</v>
+      </c>
+      <c r="E341" s="27" t="s">
+        <v>813</v>
+      </c>
+      <c r="F341" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G341" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H341" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I341" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J341" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K341" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L341" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M341" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="20">
+        <v>45740.82497931713</v>
+      </c>
+      <c r="B342" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="C342" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D342" s="21">
+        <v>2.0204124E7</v>
+      </c>
+      <c r="E342" s="21" t="s">
+        <v>815</v>
+      </c>
+      <c r="F342" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G342" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="H342" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I342" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J342" s="24">
+        <v>0.374</v>
+      </c>
+      <c r="K342" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L342" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M342" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="26">
+        <v>45740.869354490744</v>
+      </c>
+      <c r="B343" s="27" t="s">
+        <v>816</v>
+      </c>
+      <c r="C343" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D343" s="27">
+        <v>2.0202905E7</v>
+      </c>
+      <c r="E343" s="27" t="s">
+        <v>817</v>
+      </c>
+      <c r="F343" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G343" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H343" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I343" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J343" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K343" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L343" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M343" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="20">
+        <v>45740.87827393519</v>
+      </c>
+      <c r="B344" s="21" t="s">
+        <v>818</v>
+      </c>
+      <c r="C344" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D344" s="21">
+        <v>2.021291E7</v>
+      </c>
+      <c r="E344" s="21" t="s">
+        <v>819</v>
+      </c>
+      <c r="F344" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G344" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H344" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I344" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J344" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K344" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L344" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M344" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="26">
+        <v>45740.94043729166</v>
+      </c>
+      <c r="B345" s="27" t="s">
+        <v>820</v>
+      </c>
+      <c r="C345" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="D345" s="27">
+        <v>2.0223501E7</v>
+      </c>
+      <c r="E345" s="27" t="s">
+        <v>821</v>
+      </c>
+      <c r="F345" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G345" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H345" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I345" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J345" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K345" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L345" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M345" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="20">
+        <v>45740.95156753472</v>
+      </c>
+      <c r="B346" s="21" t="s">
+        <v>822</v>
+      </c>
+      <c r="C346" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D346" s="21">
+        <v>2.0242744E7</v>
+      </c>
+      <c r="E346" s="21" t="s">
+        <v>823</v>
+      </c>
+      <c r="F346" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G346" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H346" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I346" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J346" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K346" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L346" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M346" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="26">
+        <v>45740.953707974535</v>
+      </c>
+      <c r="B347" s="27" t="s">
+        <v>824</v>
+      </c>
+      <c r="C347" s="27" t="s">
+        <v>592</v>
+      </c>
+      <c r="D347" s="27">
+        <v>2.0246417E7</v>
+      </c>
+      <c r="E347" s="27" t="s">
+        <v>825</v>
+      </c>
+      <c r="F347" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G347" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H347" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I347" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J347" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K347" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L347" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M347" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="20">
+        <v>45740.95381025463</v>
+      </c>
+      <c r="B348" s="21" t="s">
+        <v>826</v>
+      </c>
+      <c r="C348" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="D348" s="21">
+        <v>2.0246428E7</v>
+      </c>
+      <c r="E348" s="21" t="s">
+        <v>827</v>
+      </c>
+      <c r="F348" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G348" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="H348" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I348" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J348" s="24">
+        <v>0.374</v>
+      </c>
+      <c r="K348" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L348" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M348" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="26">
+        <v>45740.97408059028</v>
+      </c>
+      <c r="B349" s="27" t="s">
+        <v>828</v>
+      </c>
+      <c r="C349" s="27" t="s">
+        <v>627</v>
+      </c>
+      <c r="D349" s="27">
+        <v>2.0246413E7</v>
+      </c>
+      <c r="E349" s="27" t="s">
+        <v>829</v>
+      </c>
+      <c r="F349" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G349" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H349" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I349" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J349" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K349" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L349" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M349" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="20">
+        <v>45741.00628657408</v>
+      </c>
+      <c r="B350" s="21" t="s">
+        <v>830</v>
+      </c>
+      <c r="C350" s="21" t="s">
+        <v>831</v>
+      </c>
+      <c r="D350" s="21">
+        <v>2.0253133E7</v>
+      </c>
+      <c r="E350" s="21" t="s">
+        <v>832</v>
+      </c>
+      <c r="F350" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G350" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H350" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I350" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J350" s="24">
+        <v>0.374</v>
+      </c>
+      <c r="K350" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L350" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N350" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="26">
+        <v>45741.4426891551</v>
+      </c>
+      <c r="B351" s="27" t="s">
+        <v>833</v>
+      </c>
+      <c r="C351" s="27" t="s">
+        <v>367</v>
+      </c>
+      <c r="D351" s="27">
+        <v>2.0243211E7</v>
+      </c>
+      <c r="E351" s="27" t="s">
+        <v>834</v>
+      </c>
+      <c r="F351" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G351" s="29">
+        <v>0.25</v>
+      </c>
+      <c r="H351" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I351" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J351" s="30">
+        <v>0.374</v>
+      </c>
+      <c r="K351" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L351" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M351" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="20">
+        <v>45741.56705982639</v>
+      </c>
+      <c r="B352" s="21" t="s">
+        <v>835</v>
+      </c>
+      <c r="C352" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="D352" s="21">
+        <v>2.0225279E7</v>
+      </c>
+      <c r="E352" s="21" t="s">
+        <v>836</v>
+      </c>
+      <c r="F352" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G352" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H352" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I352" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J352" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K352" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L352" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N352" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="32">
+        <v>45741.61076413194</v>
+      </c>
+      <c r="B353" s="33" t="s">
+        <v>837</v>
+      </c>
+      <c r="C353" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="D353" s="33">
+        <v>2.0242337E7</v>
+      </c>
+      <c r="E353" s="33" t="s">
+        <v>838</v>
+      </c>
+      <c r="F353" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="G353" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="H353" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I353" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J353" s="36">
+        <v>0.059</v>
+      </c>
+      <c r="K353" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="L353" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="M353" s="33" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250317.xlsx
+++ b/R/data/quiz_250317.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3182" uniqueCount="839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3344" uniqueCount="877">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2528,6 +2528,120 @@
   </si>
   <si>
     <t>이예원</t>
+  </si>
+  <si>
+    <t>kmj2542233@naver.com</t>
+  </si>
+  <si>
+    <t>ssg663927@naver.com</t>
+  </si>
+  <si>
+    <t>신성결</t>
+  </si>
+  <si>
+    <t>jmk104904@gmail.com</t>
+  </si>
+  <si>
+    <t>정민기</t>
+  </si>
+  <si>
+    <t>danieloh1216@gmail.com</t>
+  </si>
+  <si>
+    <t>오주람</t>
+  </si>
+  <si>
+    <t>psh19851985@gmail.com</t>
+  </si>
+  <si>
+    <t>박성호</t>
+  </si>
+  <si>
+    <t>hjykmj0916@gmail.com</t>
+  </si>
+  <si>
+    <t>김유경</t>
+  </si>
+  <si>
+    <t>yoonji3795@naver.com</t>
+  </si>
+  <si>
+    <t>미래융합스쿨 융합관광경영전공</t>
+  </si>
+  <si>
+    <t>김윤지</t>
+  </si>
+  <si>
+    <t>ksyoun1214@gmail.com</t>
+  </si>
+  <si>
+    <t>김승연</t>
+  </si>
+  <si>
+    <t>fireanger0@gmail.com</t>
+  </si>
+  <si>
+    <t>AI로봇융합</t>
+  </si>
+  <si>
+    <t>양조은</t>
+  </si>
+  <si>
+    <t>baekwondong@naver.com</t>
+  </si>
+  <si>
+    <t>백원동</t>
+  </si>
+  <si>
+    <t>kohhyunseo1018@naver.com</t>
+  </si>
+  <si>
+    <t>고현서</t>
+  </si>
+  <si>
+    <t>icefly1007@naver.com</t>
+  </si>
+  <si>
+    <t>우현지</t>
+  </si>
+  <si>
+    <t>qweryoon0415@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빅데이터 </t>
+  </si>
+  <si>
+    <t>ehdcks3444@naver.com</t>
+  </si>
+  <si>
+    <t>AI기술경영융합전공</t>
+  </si>
+  <si>
+    <t>김동찬</t>
+  </si>
+  <si>
+    <t>asaint84abc@gmail.com</t>
+  </si>
+  <si>
+    <t>최정우</t>
+  </si>
+  <si>
+    <t>scb0897@naver.com</t>
+  </si>
+  <si>
+    <t>신채빈</t>
+  </si>
+  <si>
+    <t>cksdudaa@gmail.com</t>
+  </si>
+  <si>
+    <t>정찬영</t>
+  </si>
+  <si>
+    <t>eunseo041320@naver.com</t>
+  </si>
+  <si>
+    <t>이은서</t>
   </si>
 </sst>
 </file>
@@ -2558,7 +2672,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border/>
     <border>
       <left style="thin">
@@ -2714,11 +2828,25 @@
         <color rgb="FF442F65"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2830,6 +2958,9 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2888,7 +3019,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N353" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N371" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -17573,44 +17704,782 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="32">
+      <c r="A353" s="26">
         <v>45741.61076413194</v>
       </c>
-      <c r="B353" s="33" t="s">
+      <c r="B353" s="27" t="s">
         <v>837</v>
       </c>
-      <c r="C353" s="33" t="s">
+      <c r="C353" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="D353" s="33">
+      <c r="D353" s="27">
         <v>2.0242337E7</v>
       </c>
-      <c r="E353" s="33" t="s">
+      <c r="E353" s="27" t="s">
         <v>838</v>
       </c>
-      <c r="F353" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="G353" s="35">
-        <v>0.2</v>
-      </c>
-      <c r="H353" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="I353" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J353" s="36">
-        <v>0.059</v>
-      </c>
-      <c r="K353" s="33" t="s">
+      <c r="F353" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G353" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H353" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I353" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J353" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K353" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="L353" s="33" t="s">
+      <c r="L353" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="M353" s="33" t="s">
+      <c r="M353" s="27" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="20">
+        <v>45741.659153333334</v>
+      </c>
+      <c r="B354" s="21" t="s">
+        <v>839</v>
+      </c>
+      <c r="C354" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D354" s="21">
+        <v>2.025271E7</v>
+      </c>
+      <c r="E354" s="21" t="s">
+        <v>688</v>
+      </c>
+      <c r="F354" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G354" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H354" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I354" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J354" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K354" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L354" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M354" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="26">
+        <v>45741.74040650463</v>
+      </c>
+      <c r="B355" s="27" t="s">
+        <v>840</v>
+      </c>
+      <c r="C355" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D355" s="27">
+        <v>2.0227026E7</v>
+      </c>
+      <c r="E355" s="27" t="s">
+        <v>841</v>
+      </c>
+      <c r="F355" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G355" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H355" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I355" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J355" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K355" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L355" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N355" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="20">
+        <v>45741.93164795139</v>
+      </c>
+      <c r="B356" s="21" t="s">
+        <v>842</v>
+      </c>
+      <c r="C356" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D356" s="21">
+        <v>2.0244144E7</v>
+      </c>
+      <c r="E356" s="21" t="s">
+        <v>843</v>
+      </c>
+      <c r="F356" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G356" s="23">
+        <v>0.25</v>
+      </c>
+      <c r="H356" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I356" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J356" s="24">
+        <v>0.374</v>
+      </c>
+      <c r="K356" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L356" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M356" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="26">
+        <v>45741.936855162035</v>
+      </c>
+      <c r="B357" s="27" t="s">
+        <v>844</v>
+      </c>
+      <c r="C357" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="D357" s="27">
+        <v>2.0243522E7</v>
+      </c>
+      <c r="E357" s="27" t="s">
+        <v>845</v>
+      </c>
+      <c r="F357" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G357" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H357" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I357" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J357" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K357" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L357" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M357" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="20">
+        <v>45741.986536192126</v>
+      </c>
+      <c r="B358" s="21" t="s">
+        <v>846</v>
+      </c>
+      <c r="C358" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="D358" s="21">
+        <v>2.0215156E7</v>
+      </c>
+      <c r="E358" s="21" t="s">
+        <v>847</v>
+      </c>
+      <c r="F358" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G358" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H358" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I358" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J358" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K358" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L358" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N358" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="26">
+        <v>45741.993177488424</v>
+      </c>
+      <c r="B359" s="27" t="s">
+        <v>848</v>
+      </c>
+      <c r="C359" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="D359" s="27">
+        <v>2.0241018E7</v>
+      </c>
+      <c r="E359" s="27" t="s">
+        <v>849</v>
+      </c>
+      <c r="F359" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G359" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H359" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I359" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J359" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K359" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L359" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M359" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="20">
+        <v>45742.00770665509</v>
+      </c>
+      <c r="B360" s="21" t="s">
+        <v>850</v>
+      </c>
+      <c r="C360" s="21" t="s">
+        <v>851</v>
+      </c>
+      <c r="D360" s="21">
+        <v>2.0227125E7</v>
+      </c>
+      <c r="E360" s="21" t="s">
+        <v>852</v>
+      </c>
+      <c r="F360" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G360" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="H360" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I360" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J360" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K360" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L360" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N360" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="26">
+        <v>45742.38781564815</v>
+      </c>
+      <c r="B361" s="27" t="s">
+        <v>853</v>
+      </c>
+      <c r="C361" s="27" t="s">
+        <v>342</v>
+      </c>
+      <c r="D361" s="27">
+        <v>2.0196405E7</v>
+      </c>
+      <c r="E361" s="27" t="s">
+        <v>854</v>
+      </c>
+      <c r="F361" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G361" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H361" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I361" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J361" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K361" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L361" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N361" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="20">
+        <v>45742.4931358912</v>
+      </c>
+      <c r="B362" s="21" t="s">
+        <v>855</v>
+      </c>
+      <c r="C362" s="21" t="s">
+        <v>856</v>
+      </c>
+      <c r="D362" s="21">
+        <v>2.0246745E7</v>
+      </c>
+      <c r="E362" s="21" t="s">
+        <v>857</v>
+      </c>
+      <c r="F362" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G362" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H362" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I362" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J362" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K362" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L362" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N362" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="26">
+        <v>45742.68479810185</v>
+      </c>
+      <c r="B363" s="27" t="s">
+        <v>858</v>
+      </c>
+      <c r="C363" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="D363" s="27">
+        <v>2.0203921E7</v>
+      </c>
+      <c r="E363" s="27" t="s">
+        <v>859</v>
+      </c>
+      <c r="F363" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G363" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H363" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I363" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J363" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K363" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L363" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N363" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="20">
+        <v>45742.69045929398</v>
+      </c>
+      <c r="B364" s="21" t="s">
+        <v>860</v>
+      </c>
+      <c r="C364" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D364" s="21">
+        <v>2.0225108E7</v>
+      </c>
+      <c r="E364" s="21" t="s">
+        <v>861</v>
+      </c>
+      <c r="F364" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G364" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H364" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I364" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J364" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K364" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L364" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M364" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="26">
+        <v>45742.717460879634</v>
+      </c>
+      <c r="B365" s="27" t="s">
+        <v>862</v>
+      </c>
+      <c r="C365" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D365" s="27">
+        <v>2.0242727E7</v>
+      </c>
+      <c r="E365" s="27" t="s">
+        <v>863</v>
+      </c>
+      <c r="F365" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G365" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H365" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I365" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J365" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K365" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L365" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N365" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="20">
+        <v>45742.72142231482</v>
+      </c>
+      <c r="B366" s="21" t="s">
+        <v>864</v>
+      </c>
+      <c r="C366" s="21" t="s">
+        <v>865</v>
+      </c>
+      <c r="D366" s="21">
+        <v>2.0245212E7</v>
+      </c>
+      <c r="E366" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="F366" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G366" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H366" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I366" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J366" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K366" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L366" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M366" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="26">
+        <v>45742.74501077546</v>
+      </c>
+      <c r="B367" s="27" t="s">
+        <v>866</v>
+      </c>
+      <c r="C367" s="27" t="s">
+        <v>867</v>
+      </c>
+      <c r="D367" s="27">
+        <v>2.0216712E7</v>
+      </c>
+      <c r="E367" s="27" t="s">
+        <v>868</v>
+      </c>
+      <c r="F367" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G367" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H367" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I367" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J367" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K367" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L367" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M367" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="20">
+        <v>45742.78465577547</v>
+      </c>
+      <c r="B368" s="21" t="s">
+        <v>869</v>
+      </c>
+      <c r="C368" s="21" t="s">
+        <v>706</v>
+      </c>
+      <c r="D368" s="21">
+        <v>2.0256785E7</v>
+      </c>
+      <c r="E368" s="21" t="s">
+        <v>870</v>
+      </c>
+      <c r="F368" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G368" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H368" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I368" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J368" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K368" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L368" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N368" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="26">
+        <v>45742.79420244213</v>
+      </c>
+      <c r="B369" s="27" t="s">
+        <v>871</v>
+      </c>
+      <c r="C369" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="D369" s="27">
+        <v>2.0243521E7</v>
+      </c>
+      <c r="E369" s="27" t="s">
+        <v>872</v>
+      </c>
+      <c r="F369" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G369" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H369" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I369" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J369" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K369" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L369" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N369" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="20">
+        <v>45742.82231113426</v>
+      </c>
+      <c r="B370" s="21" t="s">
+        <v>873</v>
+      </c>
+      <c r="C370" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D370" s="21">
+        <v>2.0213039E7</v>
+      </c>
+      <c r="E370" s="21" t="s">
+        <v>874</v>
+      </c>
+      <c r="F370" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G370" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="H370" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I370" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J370" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K370" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L370" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N370" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="32">
+        <v>45742.85027018518</v>
+      </c>
+      <c r="B371" s="33" t="s">
+        <v>875</v>
+      </c>
+      <c r="C371" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="D371" s="33">
+        <v>2.0243009E7</v>
+      </c>
+      <c r="E371" s="33" t="s">
+        <v>876</v>
+      </c>
+      <c r="F371" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="G371" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="H371" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I371" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J371" s="36">
+        <v>0.059</v>
+      </c>
+      <c r="K371" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="L371" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="N371" s="37" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250317.xlsx
+++ b/R/data/quiz_250317.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3344" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3479" uniqueCount="905">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2642,6 +2642,90 @@
   </si>
   <si>
     <t>이은서</t>
+  </si>
+  <si>
+    <t>kuen0508217@naver.com</t>
+  </si>
+  <si>
+    <t>권가영</t>
+  </si>
+  <si>
+    <t>seodonghyeong7330@gmail.com</t>
+  </si>
+  <si>
+    <t>서동형</t>
+  </si>
+  <si>
+    <t>dmsak0708@naver.com</t>
+  </si>
+  <si>
+    <t>최은임</t>
+  </si>
+  <si>
+    <t>kimjnuadad@naver.com</t>
+  </si>
+  <si>
+    <t>김도연</t>
+  </si>
+  <si>
+    <t>junsung872@gmail.com</t>
+  </si>
+  <si>
+    <t>윤준성</t>
+  </si>
+  <si>
+    <t>wookyung7536@naver.com</t>
+  </si>
+  <si>
+    <t>양우경</t>
+  </si>
+  <si>
+    <t>hyuk7515@naver.com</t>
+  </si>
+  <si>
+    <t>김동혁</t>
+  </si>
+  <si>
+    <t>seo020815@naver.com</t>
+  </si>
+  <si>
+    <t>김준서</t>
+  </si>
+  <si>
+    <t>romma37@naver.com</t>
+  </si>
+  <si>
+    <t>이새롬</t>
+  </si>
+  <si>
+    <t>imjustdaeunnnnn@gmail.com</t>
+  </si>
+  <si>
+    <t>정다은</t>
+  </si>
+  <si>
+    <t>yky9430@naver.com</t>
+  </si>
+  <si>
+    <t>유가영</t>
+  </si>
+  <si>
+    <t>taekwonlmj@gmail.com</t>
+  </si>
+  <si>
+    <t>이미주</t>
+  </si>
+  <si>
+    <t>cara0070322@gmail.com</t>
+  </si>
+  <si>
+    <t>신성민</t>
+  </si>
+  <si>
+    <t>jyjjyj057@naver.com</t>
+  </si>
+  <si>
+    <t>정예지</t>
   </si>
 </sst>
 </file>
@@ -2805,10 +2889,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -2816,13 +2900,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -2830,13 +2914,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
         <color rgb="FF442F65"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -3019,7 +3103,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N371" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N386" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -18442,43 +18526,658 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="32">
+      <c r="A371" s="26">
         <v>45742.85027018518</v>
       </c>
-      <c r="B371" s="33" t="s">
+      <c r="B371" s="27" t="s">
         <v>875</v>
       </c>
-      <c r="C371" s="33" t="s">
+      <c r="C371" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D371" s="33">
+      <c r="D371" s="27">
         <v>2.0243009E7</v>
       </c>
-      <c r="E371" s="33" t="s">
+      <c r="E371" s="27" t="s">
         <v>876</v>
       </c>
-      <c r="F371" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="G371" s="35">
-        <v>0.2</v>
-      </c>
-      <c r="H371" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="I371" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J371" s="36">
-        <v>0.059</v>
-      </c>
-      <c r="K371" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="L371" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="N371" s="37" t="s">
+      <c r="F371" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G371" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H371" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I371" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J371" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K371" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L371" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N371" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="20">
+        <v>45742.98305199074</v>
+      </c>
+      <c r="B372" s="21" t="s">
+        <v>877</v>
+      </c>
+      <c r="C372" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D372" s="21">
+        <v>2.0242909E7</v>
+      </c>
+      <c r="E372" s="21" t="s">
+        <v>878</v>
+      </c>
+      <c r="F372" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G372" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H372" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I372" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J372" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K372" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L372" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N372" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="26">
+        <v>45742.98560393519</v>
+      </c>
+      <c r="B373" s="27" t="s">
+        <v>879</v>
+      </c>
+      <c r="C373" s="27" t="s">
+        <v>380</v>
+      </c>
+      <c r="D373" s="27">
+        <v>2.0245182E7</v>
+      </c>
+      <c r="E373" s="27" t="s">
+        <v>880</v>
+      </c>
+      <c r="F373" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G373" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H373" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I373" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J373" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K373" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L373" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M373" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="20">
+        <v>45743.00355998843</v>
+      </c>
+      <c r="B374" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C374" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D374" s="21">
+        <v>2.0242328E7</v>
+      </c>
+      <c r="E374" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="F374" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G374" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H374" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I374" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J374" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K374" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L374" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N374" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="26">
+        <v>45743.06992001158</v>
+      </c>
+      <c r="B375" s="27" t="s">
+        <v>881</v>
+      </c>
+      <c r="C375" s="27" t="s">
+        <v>342</v>
+      </c>
+      <c r="D375" s="27">
+        <v>2.0225268E7</v>
+      </c>
+      <c r="E375" s="27" t="s">
+        <v>882</v>
+      </c>
+      <c r="F375" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G375" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H375" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I375" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J375" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K375" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L375" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M375" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="20">
+        <v>45743.48005885417</v>
+      </c>
+      <c r="B376" s="21" t="s">
+        <v>883</v>
+      </c>
+      <c r="C376" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D376" s="21">
+        <v>2.0241201E7</v>
+      </c>
+      <c r="E376" s="21" t="s">
+        <v>884</v>
+      </c>
+      <c r="F376" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G376" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="H376" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I376" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J376" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K376" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L376" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M376" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="26">
+        <v>45743.50034993056</v>
+      </c>
+      <c r="B377" s="27" t="s">
+        <v>885</v>
+      </c>
+      <c r="C377" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="D377" s="27">
+        <v>2.024393E7</v>
+      </c>
+      <c r="E377" s="27" t="s">
+        <v>886</v>
+      </c>
+      <c r="F377" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G377" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H377" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I377" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J377" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K377" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L377" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N377" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="20">
+        <v>45743.60360983796</v>
+      </c>
+      <c r="B378" s="21" t="s">
+        <v>887</v>
+      </c>
+      <c r="C378" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D378" s="21">
+        <v>2.0212223E7</v>
+      </c>
+      <c r="E378" s="21" t="s">
+        <v>888</v>
+      </c>
+      <c r="F378" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G378" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H378" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I378" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J378" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K378" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L378" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M378" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="26">
+        <v>45743.60863916666</v>
+      </c>
+      <c r="B379" s="27" t="s">
+        <v>889</v>
+      </c>
+      <c r="C379" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D379" s="27">
+        <v>2.0224103E7</v>
+      </c>
+      <c r="E379" s="27" t="s">
+        <v>890</v>
+      </c>
+      <c r="F379" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G379" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H379" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I379" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J379" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K379" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L379" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N379" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="20">
+        <v>45743.704392326385</v>
+      </c>
+      <c r="B380" s="21" t="s">
+        <v>891</v>
+      </c>
+      <c r="C380" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D380" s="21">
+        <v>2.0215135E7</v>
+      </c>
+      <c r="E380" s="21" t="s">
+        <v>892</v>
+      </c>
+      <c r="F380" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G380" s="23">
+        <v>0.25</v>
+      </c>
+      <c r="H380" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I380" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J380" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K380" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L380" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N380" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="26">
+        <v>45743.71384618056</v>
+      </c>
+      <c r="B381" s="27" t="s">
+        <v>893</v>
+      </c>
+      <c r="C381" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="D381" s="27">
+        <v>2.0243935E7</v>
+      </c>
+      <c r="E381" s="27" t="s">
+        <v>894</v>
+      </c>
+      <c r="F381" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G381" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H381" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I381" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J381" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K381" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L381" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M381" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="20">
+        <v>45743.71414703704</v>
+      </c>
+      <c r="B382" s="21" t="s">
+        <v>895</v>
+      </c>
+      <c r="C382" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D382" s="21">
+        <v>2.0253244E7</v>
+      </c>
+      <c r="E382" s="21" t="s">
+        <v>896</v>
+      </c>
+      <c r="F382" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G382" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H382" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I382" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J382" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K382" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L382" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M382" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="26">
+        <v>45743.72643398149</v>
+      </c>
+      <c r="B383" s="27" t="s">
+        <v>897</v>
+      </c>
+      <c r="C383" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D383" s="27">
+        <v>2.0207106E7</v>
+      </c>
+      <c r="E383" s="27" t="s">
+        <v>898</v>
+      </c>
+      <c r="F383" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G383" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H383" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I383" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J383" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K383" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L383" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M383" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="20">
+        <v>45743.762463101855</v>
+      </c>
+      <c r="B384" s="21" t="s">
+        <v>899</v>
+      </c>
+      <c r="C384" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D384" s="21">
+        <v>2.0253236E7</v>
+      </c>
+      <c r="E384" s="21" t="s">
+        <v>900</v>
+      </c>
+      <c r="F384" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G384" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H384" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I384" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J384" s="24">
+        <v>0.374</v>
+      </c>
+      <c r="K384" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L384" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M384" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="26">
+        <v>45743.82072872685</v>
+      </c>
+      <c r="B385" s="27" t="s">
+        <v>901</v>
+      </c>
+      <c r="C385" s="27" t="s">
+        <v>706</v>
+      </c>
+      <c r="D385" s="27">
+        <v>2.024674E7</v>
+      </c>
+      <c r="E385" s="27" t="s">
+        <v>902</v>
+      </c>
+      <c r="F385" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G385" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H385" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I385" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J385" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K385" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L385" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M385" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="32">
+        <v>45743.85933122685</v>
+      </c>
+      <c r="B386" s="33" t="s">
+        <v>903</v>
+      </c>
+      <c r="C386" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="D386" s="33">
+        <v>2.0213634E7</v>
+      </c>
+      <c r="E386" s="33" t="s">
+        <v>904</v>
+      </c>
+      <c r="F386" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="G386" s="35">
+        <v>0.15</v>
+      </c>
+      <c r="H386" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I386" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J386" s="36">
+        <v>0.151</v>
+      </c>
+      <c r="K386" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="L386" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="N386" s="37" t="s">
         <v>28</v>
       </c>
     </row>

--- a/R/data/quiz_250317.xlsx
+++ b/R/data/quiz_250317.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3479" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3587" uniqueCount="928">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2726,6 +2726,75 @@
   </si>
   <si>
     <t>정예지</t>
+  </si>
+  <si>
+    <t>cksal0415@gmail.com</t>
+  </si>
+  <si>
+    <t>홍찬미</t>
+  </si>
+  <si>
+    <t>hull7614@gmail.com</t>
+  </si>
+  <si>
+    <t>남궁효경</t>
+  </si>
+  <si>
+    <t>h20241202@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>h20241217@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>원예진</t>
+  </si>
+  <si>
+    <t>god303086@gmail.com</t>
+  </si>
+  <si>
+    <t>남궁연희</t>
+  </si>
+  <si>
+    <t>kheom2002@gmail.com</t>
+  </si>
+  <si>
+    <t>엄규현</t>
+  </si>
+  <si>
+    <t>a01024558927@gmail.com</t>
+  </si>
+  <si>
+    <t>정용원</t>
+  </si>
+  <si>
+    <t>rlawhdgus1212@gmail.com</t>
+  </si>
+  <si>
+    <t>김종현</t>
+  </si>
+  <si>
+    <t>gnsh2005@naver.com</t>
+  </si>
+  <si>
+    <t>이지나</t>
+  </si>
+  <si>
+    <t>subin051001@naver.com</t>
+  </si>
+  <si>
+    <t>송수빈</t>
+  </si>
+  <si>
+    <t>autumngo77@gmail.com</t>
+  </si>
+  <si>
+    <t>고나영</t>
+  </si>
+  <si>
+    <t>kses12058@gmail.com</t>
+  </si>
+  <si>
+    <t>김도현</t>
   </si>
 </sst>
 </file>
@@ -2756,7 +2825,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -2912,25 +2981,11 @@
         <color rgb="FF442F65"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3042,9 +3097,6 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3103,7 +3155,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N386" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N398" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -19141,43 +19193,535 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="32">
+      <c r="A386" s="20">
         <v>45743.85933122685</v>
       </c>
-      <c r="B386" s="33" t="s">
+      <c r="B386" s="21" t="s">
         <v>903</v>
       </c>
-      <c r="C386" s="33" t="s">
+      <c r="C386" s="21" t="s">
         <v>403</v>
       </c>
-      <c r="D386" s="33">
+      <c r="D386" s="21">
         <v>2.0213634E7</v>
       </c>
-      <c r="E386" s="33" t="s">
+      <c r="E386" s="21" t="s">
         <v>904</v>
       </c>
-      <c r="F386" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="G386" s="35">
+      <c r="F386" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G386" s="23">
         <v>0.15</v>
       </c>
-      <c r="H386" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="I386" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J386" s="36">
+      <c r="H386" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I386" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J386" s="24">
         <v>0.151</v>
       </c>
-      <c r="K386" s="33" t="s">
+      <c r="K386" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="L386" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="N386" s="37" t="s">
+      <c r="L386" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N386" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="26">
+        <v>45743.891821122685</v>
+      </c>
+      <c r="B387" s="27" t="s">
+        <v>905</v>
+      </c>
+      <c r="C387" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D387" s="27">
+        <v>2.0246941E7</v>
+      </c>
+      <c r="E387" s="27" t="s">
+        <v>906</v>
+      </c>
+      <c r="F387" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G387" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H387" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I387" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J387" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K387" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L387" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N387" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="20">
+        <v>45744.66267957176</v>
+      </c>
+      <c r="B388" s="21" t="s">
+        <v>907</v>
+      </c>
+      <c r="C388" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D388" s="21">
+        <v>2.0242218E7</v>
+      </c>
+      <c r="E388" s="21" t="s">
+        <v>908</v>
+      </c>
+      <c r="F388" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G388" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H388" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I388" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J388" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K388" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L388" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N388" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="26">
+        <v>45744.71373071759</v>
+      </c>
+      <c r="B389" s="27" t="s">
+        <v>909</v>
+      </c>
+      <c r="C389" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D389" s="27">
+        <v>2.0241202E7</v>
+      </c>
+      <c r="E389" s="27" t="s">
+        <v>757</v>
+      </c>
+      <c r="F389" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G389" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H389" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I389" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J389" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K389" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L389" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M389" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="20">
+        <v>45744.714933877316</v>
+      </c>
+      <c r="B390" s="21" t="s">
+        <v>910</v>
+      </c>
+      <c r="C390" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D390" s="21">
+        <v>2.0241217E7</v>
+      </c>
+      <c r="E390" s="21" t="s">
+        <v>911</v>
+      </c>
+      <c r="F390" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G390" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H390" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I390" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J390" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K390" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L390" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M390" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="26">
+        <v>45744.73852197916</v>
+      </c>
+      <c r="B391" s="27" t="s">
+        <v>912</v>
+      </c>
+      <c r="C391" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="D391" s="27">
+        <v>2.0227042E7</v>
+      </c>
+      <c r="E391" s="27" t="s">
+        <v>913</v>
+      </c>
+      <c r="F391" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G391" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H391" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I391" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J391" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K391" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L391" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M391" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="20">
+        <v>45744.741052743055</v>
+      </c>
+      <c r="B392" s="21" t="s">
+        <v>914</v>
+      </c>
+      <c r="C392" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D392" s="21">
+        <v>2.0212976E7</v>
+      </c>
+      <c r="E392" s="21" t="s">
+        <v>915</v>
+      </c>
+      <c r="F392" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G392" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H392" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I392" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J392" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K392" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L392" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N392" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="26">
+        <v>45744.74138037037</v>
+      </c>
+      <c r="B393" s="27" t="s">
+        <v>916</v>
+      </c>
+      <c r="C393" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D393" s="27">
+        <v>2.0242236E7</v>
+      </c>
+      <c r="E393" s="27" t="s">
+        <v>917</v>
+      </c>
+      <c r="F393" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G393" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H393" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I393" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J393" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K393" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L393" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M393" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="20">
+        <v>45744.76062045139</v>
+      </c>
+      <c r="B394" s="21" t="s">
+        <v>918</v>
+      </c>
+      <c r="C394" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D394" s="21">
+        <v>2.0192844E7</v>
+      </c>
+      <c r="E394" s="21" t="s">
+        <v>919</v>
+      </c>
+      <c r="F394" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G394" s="23">
+        <v>0.3</v>
+      </c>
+      <c r="H394" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="I394" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J394" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K394" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L394" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N394" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="26">
+        <v>45744.91521925926</v>
+      </c>
+      <c r="B395" s="27" t="s">
+        <v>920</v>
+      </c>
+      <c r="C395" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D395" s="27">
+        <v>2.024627E7</v>
+      </c>
+      <c r="E395" s="27" t="s">
+        <v>921</v>
+      </c>
+      <c r="F395" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G395" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H395" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I395" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="J395" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K395" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L395" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M395" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="20">
+        <v>45744.978252256944</v>
+      </c>
+      <c r="B396" s="21" t="s">
+        <v>922</v>
+      </c>
+      <c r="C396" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="D396" s="21">
+        <v>2.024253E7</v>
+      </c>
+      <c r="E396" s="21" t="s">
+        <v>923</v>
+      </c>
+      <c r="F396" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G396" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H396" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I396" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J396" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K396" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L396" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M396" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="26">
+        <v>45745.100416354166</v>
+      </c>
+      <c r="B397" s="27" t="s">
+        <v>924</v>
+      </c>
+      <c r="C397" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="D397" s="27">
+        <v>2.0246605E7</v>
+      </c>
+      <c r="E397" s="27" t="s">
+        <v>925</v>
+      </c>
+      <c r="F397" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G397" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H397" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I397" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J397" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K397" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L397" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N397" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="32">
+        <v>45745.17238420139</v>
+      </c>
+      <c r="B398" s="33" t="s">
+        <v>926</v>
+      </c>
+      <c r="C398" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="D398" s="33">
+        <v>2.024292E7</v>
+      </c>
+      <c r="E398" s="33" t="s">
+        <v>927</v>
+      </c>
+      <c r="F398" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="G398" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="H398" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I398" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J398" s="36">
+        <v>0.059</v>
+      </c>
+      <c r="K398" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="L398" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="M398" s="33" t="s">
         <v>28</v>
       </c>
     </row>

--- a/R/data/quiz_250317.xlsx
+++ b/R/data/quiz_250317.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3587" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3758" uniqueCount="969">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2795,6 +2795,129 @@
   </si>
   <si>
     <t>김도현</t>
+  </si>
+  <si>
+    <t>yangsj0626@gmail.com</t>
+  </si>
+  <si>
+    <t>양선준</t>
+  </si>
+  <si>
+    <t>soyeon4966@naver.com</t>
+  </si>
+  <si>
+    <t>디지털인문예술전공</t>
+  </si>
+  <si>
+    <t>김소연</t>
+  </si>
+  <si>
+    <t>kkdy1802@naver.com</t>
+  </si>
+  <si>
+    <t>ssm09093@naver.com</t>
+  </si>
+  <si>
+    <t>조준범</t>
+  </si>
+  <si>
+    <t>gbsgbsgbs01@gmail.com</t>
+  </si>
+  <si>
+    <t>인공지능 융합학부</t>
+  </si>
+  <si>
+    <t>정경환</t>
+  </si>
+  <si>
+    <t>stopji209@naver.com</t>
+  </si>
+  <si>
+    <t>정지윤</t>
+  </si>
+  <si>
+    <t>ckgustjr0705@gmail.com</t>
+  </si>
+  <si>
+    <t>차현석</t>
+  </si>
+  <si>
+    <t>ksl100101@gmail.com</t>
+  </si>
+  <si>
+    <t>김사랑</t>
+  </si>
+  <si>
+    <t>kimgg0324@naver.com</t>
+  </si>
+  <si>
+    <t>김기건</t>
+  </si>
+  <si>
+    <t>tyn47760@naver.om</t>
+  </si>
+  <si>
+    <t>권태연</t>
+  </si>
+  <si>
+    <t>csu1102@naver.com</t>
+  </si>
+  <si>
+    <t>조성운</t>
+  </si>
+  <si>
+    <t>a53309705@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체</t>
+  </si>
+  <si>
+    <t>박상훈</t>
+  </si>
+  <si>
+    <t>ysw201200@gmail.com</t>
+  </si>
+  <si>
+    <t>이윤서</t>
+  </si>
+  <si>
+    <t>hoe978034@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">식품영양학과 </t>
+  </si>
+  <si>
+    <t>이호은</t>
+  </si>
+  <si>
+    <t>hyunkyung1410@naver.com</t>
+  </si>
+  <si>
+    <t>최현경</t>
+  </si>
+  <si>
+    <t>sue92563897@gmail.com</t>
+  </si>
+  <si>
+    <t>김세연</t>
+  </si>
+  <si>
+    <t>teasu@naver.com</t>
+  </si>
+  <si>
+    <t>김태수</t>
+  </si>
+  <si>
+    <t>20242640@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>황가현</t>
+  </si>
+  <si>
+    <t>storybjy11@naver.com</t>
+  </si>
+  <si>
+    <t>박기원</t>
   </si>
 </sst>
 </file>
@@ -2825,7 +2948,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border/>
     <border>
       <left style="thin">
@@ -2958,10 +3081,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -2969,13 +3092,27 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -2985,7 +3122,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3097,6 +3234,9 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3155,7 +3295,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N398" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N417" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -19685,44 +19825,823 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="32">
+      <c r="A398" s="20">
         <v>45745.17238420139</v>
       </c>
-      <c r="B398" s="33" t="s">
+      <c r="B398" s="21" t="s">
         <v>926</v>
       </c>
-      <c r="C398" s="33" t="s">
+      <c r="C398" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D398" s="33">
+      <c r="D398" s="21">
         <v>2.024292E7</v>
       </c>
-      <c r="E398" s="33" t="s">
+      <c r="E398" s="21" t="s">
         <v>927</v>
       </c>
-      <c r="F398" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="G398" s="35">
-        <v>0.2</v>
-      </c>
-      <c r="H398" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="I398" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J398" s="36">
-        <v>0.059</v>
-      </c>
-      <c r="K398" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="L398" s="33" t="s">
+      <c r="F398" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G398" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H398" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I398" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J398" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K398" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L398" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="M398" s="33" t="s">
-        <v>28</v>
+      <c r="M398" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="26">
+        <v>45745.573546238425</v>
+      </c>
+      <c r="B399" s="27" t="s">
+        <v>928</v>
+      </c>
+      <c r="C399" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D399" s="27">
+        <v>2.0222222E7</v>
+      </c>
+      <c r="E399" s="27" t="s">
+        <v>929</v>
+      </c>
+      <c r="F399" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G399" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H399" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I399" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J399" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K399" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L399" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M399" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="20">
+        <v>45745.585222511574</v>
+      </c>
+      <c r="B400" s="21" t="s">
+        <v>930</v>
+      </c>
+      <c r="C400" s="21" t="s">
+        <v>931</v>
+      </c>
+      <c r="D400" s="21">
+        <v>2.0241705E7</v>
+      </c>
+      <c r="E400" s="21" t="s">
+        <v>932</v>
+      </c>
+      <c r="F400" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G400" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H400" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I400" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J400" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K400" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L400" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N400" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="26">
+        <v>45745.588144629626</v>
+      </c>
+      <c r="B401" s="27" t="s">
+        <v>933</v>
+      </c>
+      <c r="C401" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D401" s="27">
+        <v>2.0243208E7</v>
+      </c>
+      <c r="E401" s="27" t="s">
+        <v>884</v>
+      </c>
+      <c r="F401" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G401" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H401" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I401" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J401" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K401" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L401" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M401" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="20">
+        <v>45745.62031820602</v>
+      </c>
+      <c r="B402" s="21" t="s">
+        <v>934</v>
+      </c>
+      <c r="C402" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D402" s="21">
+        <v>2.0213353E7</v>
+      </c>
+      <c r="E402" s="21" t="s">
+        <v>935</v>
+      </c>
+      <c r="F402" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G402" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="H402" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I402" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J402" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K402" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L402" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M402" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="26">
+        <v>45745.652170625</v>
+      </c>
+      <c r="B403" s="27" t="s">
+        <v>936</v>
+      </c>
+      <c r="C403" s="27" t="s">
+        <v>937</v>
+      </c>
+      <c r="D403" s="27">
+        <v>2.0256773E7</v>
+      </c>
+      <c r="E403" s="27" t="s">
+        <v>938</v>
+      </c>
+      <c r="F403" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G403" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H403" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I403" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J403" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K403" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L403" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M403" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="20">
+        <v>45745.66570194444</v>
+      </c>
+      <c r="B404" s="21" t="s">
+        <v>939</v>
+      </c>
+      <c r="C404" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D404" s="21">
+        <v>2.0227074E7</v>
+      </c>
+      <c r="E404" s="21" t="s">
+        <v>940</v>
+      </c>
+      <c r="F404" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G404" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H404" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I404" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J404" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K404" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L404" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M404" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="26">
+        <v>45745.69036582176</v>
+      </c>
+      <c r="B405" s="27" t="s">
+        <v>941</v>
+      </c>
+      <c r="C405" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D405" s="27">
+        <v>2.024629E7</v>
+      </c>
+      <c r="E405" s="27" t="s">
+        <v>942</v>
+      </c>
+      <c r="F405" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G405" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H405" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I405" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J405" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K405" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L405" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N405" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="20">
+        <v>45745.72937649305</v>
+      </c>
+      <c r="B406" s="21" t="s">
+        <v>943</v>
+      </c>
+      <c r="C406" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D406" s="21">
+        <v>2.024231E7</v>
+      </c>
+      <c r="E406" s="21" t="s">
+        <v>944</v>
+      </c>
+      <c r="F406" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G406" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H406" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I406" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J406" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K406" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L406" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N406" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="26">
+        <v>45745.730322372685</v>
+      </c>
+      <c r="B407" s="27" t="s">
+        <v>945</v>
+      </c>
+      <c r="C407" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D407" s="27">
+        <v>2.0242917E7</v>
+      </c>
+      <c r="E407" s="27" t="s">
+        <v>946</v>
+      </c>
+      <c r="F407" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G407" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H407" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I407" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J407" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K407" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L407" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M407" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="20">
+        <v>45745.73244320602</v>
+      </c>
+      <c r="B408" s="21" t="s">
+        <v>947</v>
+      </c>
+      <c r="C408" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D408" s="21">
+        <v>2.0246212E7</v>
+      </c>
+      <c r="E408" s="21" t="s">
+        <v>948</v>
+      </c>
+      <c r="F408" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G408" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H408" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I408" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J408" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K408" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L408" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N408" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="26">
+        <v>45745.77284369213</v>
+      </c>
+      <c r="B409" s="27" t="s">
+        <v>949</v>
+      </c>
+      <c r="C409" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D409" s="27">
+        <v>2.0223044E7</v>
+      </c>
+      <c r="E409" s="27" t="s">
+        <v>950</v>
+      </c>
+      <c r="F409" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G409" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H409" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I409" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J409" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K409" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L409" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N409" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="20">
+        <v>45745.80510748843</v>
+      </c>
+      <c r="B410" s="21" t="s">
+        <v>951</v>
+      </c>
+      <c r="C410" s="21" t="s">
+        <v>952</v>
+      </c>
+      <c r="D410" s="21">
+        <v>2.0243317E7</v>
+      </c>
+      <c r="E410" s="21" t="s">
+        <v>953</v>
+      </c>
+      <c r="F410" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G410" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H410" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I410" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J410" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K410" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L410" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M410" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="26">
+        <v>45745.85816366898</v>
+      </c>
+      <c r="B411" s="27" t="s">
+        <v>954</v>
+      </c>
+      <c r="C411" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D411" s="27">
+        <v>2.0212556E7</v>
+      </c>
+      <c r="E411" s="27" t="s">
+        <v>955</v>
+      </c>
+      <c r="F411" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G411" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H411" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I411" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J411" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K411" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L411" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N411" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="20">
+        <v>45745.86680737269</v>
+      </c>
+      <c r="B412" s="21" t="s">
+        <v>956</v>
+      </c>
+      <c r="C412" s="21" t="s">
+        <v>957</v>
+      </c>
+      <c r="D412" s="21">
+        <v>2.0243837E7</v>
+      </c>
+      <c r="E412" s="21" t="s">
+        <v>958</v>
+      </c>
+      <c r="F412" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G412" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H412" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I412" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J412" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K412" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L412" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N412" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="26">
+        <v>45745.88211046296</v>
+      </c>
+      <c r="B413" s="27" t="s">
+        <v>959</v>
+      </c>
+      <c r="C413" s="27" t="s">
+        <v>665</v>
+      </c>
+      <c r="D413" s="27">
+        <v>2.0242583E7</v>
+      </c>
+      <c r="E413" s="27" t="s">
+        <v>960</v>
+      </c>
+      <c r="F413" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G413" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H413" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I413" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J413" s="30">
+        <v>0.374</v>
+      </c>
+      <c r="K413" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L413" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N413" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="20">
+        <v>45745.89625075231</v>
+      </c>
+      <c r="B414" s="21" t="s">
+        <v>961</v>
+      </c>
+      <c r="C414" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="D414" s="21">
+        <v>2.0241015E7</v>
+      </c>
+      <c r="E414" s="21" t="s">
+        <v>962</v>
+      </c>
+      <c r="F414" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G414" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="H414" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I414" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="J414" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K414" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L414" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M414" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="26">
+        <v>45745.930431099536</v>
+      </c>
+      <c r="B415" s="27" t="s">
+        <v>963</v>
+      </c>
+      <c r="C415" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D415" s="27">
+        <v>2.0242708E7</v>
+      </c>
+      <c r="E415" s="27" t="s">
+        <v>964</v>
+      </c>
+      <c r="F415" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G415" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H415" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I415" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J415" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K415" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L415" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N415" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="20">
+        <v>45745.948167546296</v>
+      </c>
+      <c r="B416" s="21" t="s">
+        <v>965</v>
+      </c>
+      <c r="C416" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D416" s="21">
+        <v>2.024264E7</v>
+      </c>
+      <c r="E416" s="21" t="s">
+        <v>966</v>
+      </c>
+      <c r="F416" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G416" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H416" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I416" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J416" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K416" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L416" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M416" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="32">
+        <v>45745.95006956019</v>
+      </c>
+      <c r="B417" s="33" t="s">
+        <v>967</v>
+      </c>
+      <c r="C417" s="33" t="s">
+        <v>512</v>
+      </c>
+      <c r="D417" s="33">
+        <v>2.0191615E7</v>
+      </c>
+      <c r="E417" s="33" t="s">
+        <v>968</v>
+      </c>
+      <c r="F417" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G417" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="H417" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I417" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J417" s="36">
+        <v>0.059</v>
+      </c>
+      <c r="K417" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="L417" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="N417" s="37" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250317.xlsx
+++ b/R/data/quiz_250317.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3758" uniqueCount="969">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5018" uniqueCount="1255">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2918,6 +2918,864 @@
   </si>
   <si>
     <t>박기원</t>
+  </si>
+  <si>
+    <t>dltjdgns040528@naver.com</t>
+  </si>
+  <si>
+    <t>이성훈</t>
+  </si>
+  <si>
+    <t>thd2270@gmail.com</t>
+  </si>
+  <si>
+    <t>강예송</t>
+  </si>
+  <si>
+    <t>jbh7574@naver.com</t>
+  </si>
+  <si>
+    <t>전병훈</t>
+  </si>
+  <si>
+    <t>es187019@gmail.com</t>
+  </si>
+  <si>
+    <t>김현빈</t>
+  </si>
+  <si>
+    <t>leesojin0000@naver.com</t>
+  </si>
+  <si>
+    <t>이소진</t>
+  </si>
+  <si>
+    <t>lminseok1228@gmail.com</t>
+  </si>
+  <si>
+    <t>이민석</t>
+  </si>
+  <si>
+    <t>in4394@naver.com</t>
+  </si>
+  <si>
+    <t>김혜인</t>
+  </si>
+  <si>
+    <t>rga0801@naver.com</t>
+  </si>
+  <si>
+    <t>김형민</t>
+  </si>
+  <si>
+    <t>difeded@naver.com</t>
+  </si>
+  <si>
+    <t>박혜인</t>
+  </si>
+  <si>
+    <t>eshan0401@gmail.com</t>
+  </si>
+  <si>
+    <t>한은성</t>
+  </si>
+  <si>
+    <t>de3230@naver.com</t>
+  </si>
+  <si>
+    <t>정대현</t>
+  </si>
+  <si>
+    <t>dlwngud77777@naver.com</t>
+  </si>
+  <si>
+    <t>이주형</t>
+  </si>
+  <si>
+    <t>woojinkim0518@naver.com</t>
+  </si>
+  <si>
+    <t>김우진</t>
+  </si>
+  <si>
+    <t>min88278610@gmail.com</t>
+  </si>
+  <si>
+    <t>민선주</t>
+  </si>
+  <si>
+    <t>juseung1449@naver.com</t>
+  </si>
+  <si>
+    <t>이주승</t>
+  </si>
+  <si>
+    <t>yooyoungjune@naver.com</t>
+  </si>
+  <si>
+    <t>유영준</t>
+  </si>
+  <si>
+    <t>kim1123693@gmail.com</t>
+  </si>
+  <si>
+    <t>김희수</t>
+  </si>
+  <si>
+    <t>tengentoppa0641@gmail.com</t>
+  </si>
+  <si>
+    <t>이정민</t>
+  </si>
+  <si>
+    <t>kim9301204@gmail.com</t>
+  </si>
+  <si>
+    <t>소대현</t>
+  </si>
+  <si>
+    <t>cheolhyun1234@naver.com</t>
+  </si>
+  <si>
+    <t>박철현</t>
+  </si>
+  <si>
+    <t>alex1874@naver.com</t>
+  </si>
+  <si>
+    <t>김진수</t>
+  </si>
+  <si>
+    <t>song_050929@naver.com</t>
+  </si>
+  <si>
+    <t>송은채</t>
+  </si>
+  <si>
+    <t>j92921652@gmail.com</t>
+  </si>
+  <si>
+    <t>정주원</t>
+  </si>
+  <si>
+    <t>dhhhxh273@naver.com</t>
+  </si>
+  <si>
+    <t>최서정</t>
+  </si>
+  <si>
+    <t>000727yjh@naver.com</t>
+  </si>
+  <si>
+    <t>윤종현</t>
+  </si>
+  <si>
+    <t>kec0705@naver.com</t>
+  </si>
+  <si>
+    <t>인공지능융합학부 Ai의료</t>
+  </si>
+  <si>
+    <t>이은영</t>
+  </si>
+  <si>
+    <t>jwseok0218@naver.com</t>
+  </si>
+  <si>
+    <t>조우석</t>
+  </si>
+  <si>
+    <t>boeun050214@naver.com</t>
+  </si>
+  <si>
+    <t>이보은</t>
+  </si>
+  <si>
+    <t>lhp050705@gmail.com</t>
+  </si>
+  <si>
+    <t>이현표</t>
+  </si>
+  <si>
+    <t>nahm63@naver.com</t>
+  </si>
+  <si>
+    <t>인문학부 철학전공</t>
+  </si>
+  <si>
+    <t>김남엽</t>
+  </si>
+  <si>
+    <t>kosac99-@naver.com</t>
+  </si>
+  <si>
+    <t>김성희</t>
+  </si>
+  <si>
+    <t>a.to.the.z.1087@gmail.com</t>
+  </si>
+  <si>
+    <t>김지혜</t>
+  </si>
+  <si>
+    <t>bluelion-gbn9981@naver.com</t>
+  </si>
+  <si>
+    <t>구보늬</t>
+  </si>
+  <si>
+    <t>ratso6113@gmail.com</t>
+  </si>
+  <si>
+    <t>이소연</t>
+  </si>
+  <si>
+    <t>rlaqufl1234@naver.com</t>
+  </si>
+  <si>
+    <t>김벼리</t>
+  </si>
+  <si>
+    <t>ahyeon8650@naver.com</t>
+  </si>
+  <si>
+    <t>서아현</t>
+  </si>
+  <si>
+    <t>yu760923@naver.com</t>
+  </si>
+  <si>
+    <t>노윤희</t>
+  </si>
+  <si>
+    <t>zouyuanyuan0101@gmail.com</t>
+  </si>
+  <si>
+    <t>문화산업</t>
+  </si>
+  <si>
+    <t>ZOU YUANYUAN</t>
+  </si>
+  <si>
+    <t>skgurwls0416@gmail.com</t>
+  </si>
+  <si>
+    <t>나혁진</t>
+  </si>
+  <si>
+    <t>opopkang0528@gmail.com</t>
+  </si>
+  <si>
+    <t>강현지</t>
+  </si>
+  <si>
+    <t>kimminjung6615@hanmail.net</t>
+  </si>
+  <si>
+    <t>gyuha8489@gmail.com</t>
+  </si>
+  <si>
+    <t>김유하</t>
+  </si>
+  <si>
+    <t>kijoopark12@gmail.com</t>
+  </si>
+  <si>
+    <t>박기주</t>
+  </si>
+  <si>
+    <t>jjongwoo0628@naver.com</t>
+  </si>
+  <si>
+    <t>윤종우</t>
+  </si>
+  <si>
+    <t>seoulsion123@gmail.com</t>
+  </si>
+  <si>
+    <t>러사아학과</t>
+  </si>
+  <si>
+    <t>chrisjuice@naver.com</t>
+  </si>
+  <si>
+    <t>한수민</t>
+  </si>
+  <si>
+    <t>kim9876584@gmail.com</t>
+  </si>
+  <si>
+    <t>김성욱</t>
+  </si>
+  <si>
+    <t>leedaeun0409@naver.com</t>
+  </si>
+  <si>
+    <t>hmsimlk@naver.com</t>
+  </si>
+  <si>
+    <t>홍수민</t>
+  </si>
+  <si>
+    <t>minseo1416@naver.com</t>
+  </si>
+  <si>
+    <t>권민서</t>
+  </si>
+  <si>
+    <t>namjihk@gmail.com</t>
+  </si>
+  <si>
+    <t>남지혁</t>
+  </si>
+  <si>
+    <t>dlwldn010108@naver.com</t>
+  </si>
+  <si>
+    <t>Ai로봇융합전공</t>
+  </si>
+  <si>
+    <t>이지우</t>
+  </si>
+  <si>
+    <t>hanmaim89@gmail.com</t>
+  </si>
+  <si>
+    <t>h20241235@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>정채원</t>
+  </si>
+  <si>
+    <t>janghs476@gmail.com</t>
+  </si>
+  <si>
+    <t>장현서</t>
+  </si>
+  <si>
+    <t>juicee220@gmail.com</t>
+  </si>
+  <si>
+    <t>최주아</t>
+  </si>
+  <si>
+    <t>qkrwndus1117@naver.com</t>
+  </si>
+  <si>
+    <t>박주연</t>
+  </si>
+  <si>
+    <t>ujaehong122@gmail.com</t>
+  </si>
+  <si>
+    <t>사학전공</t>
+  </si>
+  <si>
+    <t>우재홍</t>
+  </si>
+  <si>
+    <t>psb051014@gmail.com</t>
+  </si>
+  <si>
+    <t>박수빈</t>
+  </si>
+  <si>
+    <t>dojun0707@naver.com</t>
+  </si>
+  <si>
+    <t>빅데이터 전공</t>
+  </si>
+  <si>
+    <t>차도준</t>
+  </si>
+  <si>
+    <t>qkrwogus030103@naver.com</t>
+  </si>
+  <si>
+    <t>박재현</t>
+  </si>
+  <si>
+    <t>sswe29772977@gmail.com</t>
+  </si>
+  <si>
+    <t>성승원</t>
+  </si>
+  <si>
+    <t>sinsujin0121@gmail.com</t>
+  </si>
+  <si>
+    <t>신수진</t>
+  </si>
+  <si>
+    <t>hyeri051119@naver.com</t>
+  </si>
+  <si>
+    <t>서혜리</t>
+  </si>
+  <si>
+    <t>g01086348696@gmail.com</t>
+  </si>
+  <si>
+    <t>박선근</t>
+  </si>
+  <si>
+    <t>a01033294075@gmail.com</t>
+  </si>
+  <si>
+    <t>임혜원</t>
+  </si>
+  <si>
+    <t>sop1210805@gmail.com</t>
+  </si>
+  <si>
+    <t>이정진</t>
+  </si>
+  <si>
+    <t>eugenejung0324@gmail.com</t>
+  </si>
+  <si>
+    <t>정지호</t>
+  </si>
+  <si>
+    <t>astpqls3541@naver.com</t>
+  </si>
+  <si>
+    <t>이세빈</t>
+  </si>
+  <si>
+    <t>alexwoojin17@gmail.com</t>
+  </si>
+  <si>
+    <t>차우진</t>
+  </si>
+  <si>
+    <t>gin050302@naver.com</t>
+  </si>
+  <si>
+    <t>김현정</t>
+  </si>
+  <si>
+    <t>lcs7714567@naver.com</t>
+  </si>
+  <si>
+    <t>pyr0528@naver.com</t>
+  </si>
+  <si>
+    <t>박예린</t>
+  </si>
+  <si>
+    <t>seojungbin050928@naver.com</t>
+  </si>
+  <si>
+    <t>서정빈</t>
+  </si>
+  <si>
+    <t>pohang0209@gmail.com</t>
+  </si>
+  <si>
+    <t>이성희</t>
+  </si>
+  <si>
+    <t>tldkwhgsl@gmail.com</t>
+  </si>
+  <si>
+    <t>최다온</t>
+  </si>
+  <si>
+    <t>nmi123nmi0212@gmail.com</t>
+  </si>
+  <si>
+    <t>노현주</t>
+  </si>
+  <si>
+    <t>soeun7443@naver.com</t>
+  </si>
+  <si>
+    <t>박소은</t>
+  </si>
+  <si>
+    <t>jonghyeogc126@gmail.com</t>
+  </si>
+  <si>
+    <t>최종혁</t>
+  </si>
+  <si>
+    <t>juni060919@naver.com</t>
+  </si>
+  <si>
+    <t>언어청각학부</t>
+  </si>
+  <si>
+    <t>이주은</t>
+  </si>
+  <si>
+    <t>parkjuheok0420@gmail.com</t>
+  </si>
+  <si>
+    <t>박주혁</t>
+  </si>
+  <si>
+    <t>dlwntkd3526@naver.com</t>
+  </si>
+  <si>
+    <t>이주상</t>
+  </si>
+  <si>
+    <t>nkav1234@naver.com</t>
+  </si>
+  <si>
+    <t>박종민</t>
+  </si>
+  <si>
+    <t>leeds44@naver.com</t>
+  </si>
+  <si>
+    <t>빅데이터과</t>
+  </si>
+  <si>
+    <t>이동수</t>
+  </si>
+  <si>
+    <t>jahee0114@gmail.com</t>
+  </si>
+  <si>
+    <t>최재희</t>
+  </si>
+  <si>
+    <t>hby9364@naver.com</t>
+  </si>
+  <si>
+    <t>황보연</t>
+  </si>
+  <si>
+    <t>rhdbswn01@naver.com</t>
+  </si>
+  <si>
+    <t>언론방송융합미디어학과</t>
+  </si>
+  <si>
+    <t>고윤주</t>
+  </si>
+  <si>
+    <t>pgueue110@gmail.com</t>
+  </si>
+  <si>
+    <t>정다영</t>
+  </si>
+  <si>
+    <t>2013bin@naver.com</t>
+  </si>
+  <si>
+    <t>박유빈</t>
+  </si>
+  <si>
+    <t>solyooncho@naver.com</t>
+  </si>
+  <si>
+    <t>조윤솔</t>
+  </si>
+  <si>
+    <t>ehrud6450@naver.com</t>
+  </si>
+  <si>
+    <t>황도경</t>
+  </si>
+  <si>
+    <t>crescent0221@naver.com</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>오상현</t>
+  </si>
+  <si>
+    <t>moonsy06@naver.com</t>
+  </si>
+  <si>
+    <t>문소연</t>
+  </si>
+  <si>
+    <t>dldudals0413@naver.com</t>
+  </si>
+  <si>
+    <t>이영민</t>
+  </si>
+  <si>
+    <t>minser9265@gmail.com</t>
+  </si>
+  <si>
+    <t>ujinhong11@gmail.com</t>
+  </si>
+  <si>
+    <t>홍우진</t>
+  </si>
+  <si>
+    <t>dbsrhkdid5@naver.com</t>
+  </si>
+  <si>
+    <t>박태양</t>
+  </si>
+  <si>
+    <t>hclee2891@naver.com</t>
+  </si>
+  <si>
+    <t>이학찬</t>
+  </si>
+  <si>
+    <t>english3849@naver.com</t>
+  </si>
+  <si>
+    <t>장서린</t>
+  </si>
+  <si>
+    <t>kay202801@naver.com</t>
+  </si>
+  <si>
+    <t>김아영</t>
+  </si>
+  <si>
+    <t>kykim0117@gmail.com</t>
+  </si>
+  <si>
+    <t>김규연</t>
+  </si>
+  <si>
+    <t>qga0303@naver.com</t>
+  </si>
+  <si>
+    <t>박하민</t>
+  </si>
+  <si>
+    <t>fnaf0039@gmail.com</t>
+  </si>
+  <si>
+    <t>박건도</t>
+  </si>
+  <si>
+    <t>seahorse93076714@gmail.com</t>
+  </si>
+  <si>
+    <t>이지원</t>
+  </si>
+  <si>
+    <t>ohyegon050824@gmail.com</t>
+  </si>
+  <si>
+    <t>오예건</t>
+  </si>
+  <si>
+    <t>isleehyun@gmail.com</t>
+  </si>
+  <si>
+    <t>이승현</t>
+  </si>
+  <si>
+    <t>chlwodlf9557@naver.com</t>
+  </si>
+  <si>
+    <t>최재일</t>
+  </si>
+  <si>
+    <t>bjfcu7@gmail.com</t>
+  </si>
+  <si>
+    <t>김채연</t>
+  </si>
+  <si>
+    <t>mgim4774@gmail.com</t>
+  </si>
+  <si>
+    <t>김진엽</t>
+  </si>
+  <si>
+    <t>wjdgksdla@naver.com</t>
+  </si>
+  <si>
+    <t>이정한</t>
+  </si>
+  <si>
+    <t>lyb051211-@naver.com</t>
+  </si>
+  <si>
+    <t>이예빈</t>
+  </si>
+  <si>
+    <t>rlacodms0906@naver.com</t>
+  </si>
+  <si>
+    <t>김채은</t>
+  </si>
+  <si>
+    <t>tkdahrrlf02@gmail.com</t>
+  </si>
+  <si>
+    <t>길상목</t>
+  </si>
+  <si>
+    <t>dami1232@naver.com</t>
+  </si>
+  <si>
+    <t>김경재</t>
+  </si>
+  <si>
+    <t>alwodtkfkd3@gmail.com</t>
+  </si>
+  <si>
+    <t>배승제</t>
+  </si>
+  <si>
+    <t>jae2001830@gmail.com</t>
+  </si>
+  <si>
+    <t>생명과확과</t>
+  </si>
+  <si>
+    <t>이재홍</t>
+  </si>
+  <si>
+    <t>djun321@naver.com</t>
+  </si>
+  <si>
+    <t>광고홍보</t>
+  </si>
+  <si>
+    <t>황동준</t>
+  </si>
+  <si>
+    <t>hallym20246626@gmail.com</t>
+  </si>
+  <si>
+    <t>백송헌</t>
+  </si>
+  <si>
+    <t>kar0173@naver.com</t>
+  </si>
+  <si>
+    <t>최승민</t>
+  </si>
+  <si>
+    <t>baagle007@gmail.com</t>
+  </si>
+  <si>
+    <t>박도은</t>
+  </si>
+  <si>
+    <t>cntmddl1@naver.com</t>
+  </si>
+  <si>
+    <t>국어국문학전공</t>
+  </si>
+  <si>
+    <t>추승이</t>
+  </si>
+  <si>
+    <t>bsj021105@naver.com</t>
+  </si>
+  <si>
+    <t>백수정</t>
+  </si>
+  <si>
+    <t>roytoy151827@gmail.com</t>
+  </si>
+  <si>
+    <t>김용한</t>
+  </si>
+  <si>
+    <t>wjdtjdbs8926@naver.com</t>
+  </si>
+  <si>
+    <t>lim48664401@gmail.com</t>
+  </si>
+  <si>
+    <t>임동욱</t>
+  </si>
+  <si>
+    <t>abck0612@naver.com</t>
+  </si>
+  <si>
+    <t>서예림</t>
+  </si>
+  <si>
+    <t>hey.seokjae@gmail.com</t>
+  </si>
+  <si>
+    <t>황석재</t>
+  </si>
+  <si>
+    <t>choiseoungbin@gmail.com</t>
+  </si>
+  <si>
+    <t>최승빈</t>
+  </si>
+  <si>
+    <t>selliakim@gmail.com</t>
+  </si>
+  <si>
+    <t>김수아</t>
+  </si>
+  <si>
+    <t>goseokran051021@gmail.com</t>
+  </si>
+  <si>
+    <t>고석란</t>
+  </si>
+  <si>
+    <t>jaenn103@naver.com</t>
+  </si>
+  <si>
+    <t>김재원</t>
+  </si>
+  <si>
+    <t>dfhirtywk@gmail.com</t>
+  </si>
+  <si>
+    <t>최세현</t>
+  </si>
+  <si>
+    <t>yuri060314@naver.com</t>
+  </si>
+  <si>
+    <t>정유리</t>
+  </si>
+  <si>
+    <t>dldmstj1027@gmail.com</t>
+  </si>
+  <si>
+    <t>monica.oh0609@gmail.com</t>
+  </si>
+  <si>
+    <t>오민선</t>
+  </si>
+  <si>
+    <t>gagahyun335@naver.com</t>
+  </si>
+  <si>
+    <t>이가현</t>
+  </si>
+  <si>
+    <t>chlehdgk0404@naver.com</t>
+  </si>
+  <si>
+    <t>최동하</t>
+  </si>
+  <si>
+    <t>jaeyoon1163@naver.com</t>
+  </si>
+  <si>
+    <t>정재윤</t>
+  </si>
+  <si>
+    <t>xhsh030408@naver.com</t>
+  </si>
+  <si>
+    <t>황성현</t>
+  </si>
+  <si>
+    <t>20215177@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>신승훈</t>
   </si>
 </sst>
 </file>
@@ -2948,7 +3806,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -3104,25 +3962,11 @@
         <color rgb="FF442F65"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3234,9 +4078,6 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3295,7 +4136,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N417" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N557" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -20604,44 +21445,5784 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="32">
+      <c r="A417" s="26">
         <v>45745.95006956019</v>
       </c>
-      <c r="B417" s="33" t="s">
+      <c r="B417" s="27" t="s">
         <v>967</v>
       </c>
-      <c r="C417" s="33" t="s">
+      <c r="C417" s="27" t="s">
         <v>512</v>
       </c>
-      <c r="D417" s="33">
+      <c r="D417" s="27">
         <v>2.0191615E7</v>
       </c>
-      <c r="E417" s="33" t="s">
+      <c r="E417" s="27" t="s">
         <v>968</v>
       </c>
-      <c r="F417" s="34" t="s">
+      <c r="F417" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G417" s="35">
-        <v>0.2</v>
-      </c>
-      <c r="H417" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="I417" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J417" s="36">
-        <v>0.059</v>
-      </c>
-      <c r="K417" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="L417" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="N417" s="37" t="s">
+      <c r="G417" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H417" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I417" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J417" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K417" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L417" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N417" s="31" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="20">
+        <v>45745.95582643518</v>
+      </c>
+      <c r="B418" s="21" t="s">
+        <v>969</v>
+      </c>
+      <c r="C418" s="21" t="s">
+        <v>497</v>
+      </c>
+      <c r="D418" s="21">
+        <v>2.0231716E7</v>
+      </c>
+      <c r="E418" s="21" t="s">
+        <v>970</v>
+      </c>
+      <c r="F418" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G418" s="23">
+        <v>0.3</v>
+      </c>
+      <c r="H418" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I418" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J418" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K418" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L418" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M418" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="26">
+        <v>45745.97208466435</v>
+      </c>
+      <c r="B419" s="27" t="s">
+        <v>971</v>
+      </c>
+      <c r="C419" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D419" s="27">
+        <v>2.0243701E7</v>
+      </c>
+      <c r="E419" s="27" t="s">
+        <v>972</v>
+      </c>
+      <c r="F419" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G419" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H419" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I419" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J419" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K419" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L419" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M419" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="20">
+        <v>45745.972897893516</v>
+      </c>
+      <c r="B420" s="21" t="s">
+        <v>973</v>
+      </c>
+      <c r="C420" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D420" s="21">
+        <v>2.0183242E7</v>
+      </c>
+      <c r="E420" s="21" t="s">
+        <v>974</v>
+      </c>
+      <c r="F420" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G420" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H420" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I420" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J420" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K420" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L420" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N420" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="26">
+        <v>45745.97575557871</v>
+      </c>
+      <c r="B421" s="27" t="s">
+        <v>975</v>
+      </c>
+      <c r="C421" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D421" s="27">
+        <v>2.0242715E7</v>
+      </c>
+      <c r="E421" s="27" t="s">
+        <v>976</v>
+      </c>
+      <c r="F421" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G421" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H421" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I421" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J421" s="30">
+        <v>0.002</v>
+      </c>
+      <c r="K421" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="L421" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N421" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="20">
+        <v>45745.99381292824</v>
+      </c>
+      <c r="B422" s="21" t="s">
+        <v>977</v>
+      </c>
+      <c r="C422" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D422" s="21">
+        <v>2.0242553E7</v>
+      </c>
+      <c r="E422" s="21" t="s">
+        <v>978</v>
+      </c>
+      <c r="F422" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G422" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H422" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I422" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J422" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K422" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L422" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N422" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="26">
+        <v>45746.0043849537</v>
+      </c>
+      <c r="B423" s="27" t="s">
+        <v>979</v>
+      </c>
+      <c r="C423" s="27" t="s">
+        <v>380</v>
+      </c>
+      <c r="D423" s="27">
+        <v>2.0245219E7</v>
+      </c>
+      <c r="E423" s="27" t="s">
+        <v>980</v>
+      </c>
+      <c r="F423" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G423" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H423" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I423" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J423" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K423" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L423" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N423" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="20">
+        <v>45746.018961354166</v>
+      </c>
+      <c r="B424" s="21" t="s">
+        <v>981</v>
+      </c>
+      <c r="C424" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D424" s="21">
+        <v>2.0232323E7</v>
+      </c>
+      <c r="E424" s="21" t="s">
+        <v>982</v>
+      </c>
+      <c r="F424" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G424" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H424" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I424" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J424" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K424" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L424" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N424" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="26">
+        <v>45746.019633344906</v>
+      </c>
+      <c r="B425" s="27" t="s">
+        <v>983</v>
+      </c>
+      <c r="C425" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="D425" s="27">
+        <v>2.0215146E7</v>
+      </c>
+      <c r="E425" s="27" t="s">
+        <v>984</v>
+      </c>
+      <c r="F425" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G425" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H425" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I425" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J425" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K425" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L425" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M425" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="20">
+        <v>45746.05171063657</v>
+      </c>
+      <c r="B426" s="21" t="s">
+        <v>985</v>
+      </c>
+      <c r="C426" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D426" s="21">
+        <v>2.0242967E7</v>
+      </c>
+      <c r="E426" s="21" t="s">
+        <v>986</v>
+      </c>
+      <c r="F426" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G426" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H426" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I426" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J426" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K426" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L426" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M426" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="26">
+        <v>45746.05682591435</v>
+      </c>
+      <c r="B427" s="27" t="s">
+        <v>987</v>
+      </c>
+      <c r="C427" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="D427" s="27">
+        <v>2.0242585E7</v>
+      </c>
+      <c r="E427" s="27" t="s">
+        <v>988</v>
+      </c>
+      <c r="F427" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G427" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H427" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I427" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J427" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K427" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L427" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M427" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="20">
+        <v>45746.06902659722</v>
+      </c>
+      <c r="B428" s="21" t="s">
+        <v>989</v>
+      </c>
+      <c r="C428" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="D428" s="21">
+        <v>2.0243348E7</v>
+      </c>
+      <c r="E428" s="21" t="s">
+        <v>990</v>
+      </c>
+      <c r="F428" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G428" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H428" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I428" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J428" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K428" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L428" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M428" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="26">
+        <v>45746.081921296296</v>
+      </c>
+      <c r="B429" s="27" t="s">
+        <v>991</v>
+      </c>
+      <c r="C429" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D429" s="27">
+        <v>2.0194143E7</v>
+      </c>
+      <c r="E429" s="27" t="s">
+        <v>992</v>
+      </c>
+      <c r="F429" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G429" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H429" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I429" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J429" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K429" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L429" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M429" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="20">
+        <v>45746.084942546295</v>
+      </c>
+      <c r="B430" s="21" t="s">
+        <v>993</v>
+      </c>
+      <c r="C430" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D430" s="21">
+        <v>2.0203308E7</v>
+      </c>
+      <c r="E430" s="21" t="s">
+        <v>994</v>
+      </c>
+      <c r="F430" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G430" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H430" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I430" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J430" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K430" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L430" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M430" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="26">
+        <v>45746.13663144676</v>
+      </c>
+      <c r="B431" s="27" t="s">
+        <v>995</v>
+      </c>
+      <c r="C431" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D431" s="27">
+        <v>2.0242615E7</v>
+      </c>
+      <c r="E431" s="27" t="s">
+        <v>996</v>
+      </c>
+      <c r="F431" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G431" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H431" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I431" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J431" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K431" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L431" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N431" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="20">
+        <v>45746.17176053241</v>
+      </c>
+      <c r="B432" s="21" t="s">
+        <v>997</v>
+      </c>
+      <c r="C432" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D432" s="21">
+        <v>2.0203726E7</v>
+      </c>
+      <c r="E432" s="21" t="s">
+        <v>998</v>
+      </c>
+      <c r="F432" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G432" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H432" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I432" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J432" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K432" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L432" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M432" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="26">
+        <v>45746.24469493056</v>
+      </c>
+      <c r="B433" s="27" t="s">
+        <v>999</v>
+      </c>
+      <c r="C433" s="27" t="s">
+        <v>706</v>
+      </c>
+      <c r="D433" s="27">
+        <v>2.0216739E7</v>
+      </c>
+      <c r="E433" s="27" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F433" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G433" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H433" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I433" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J433" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K433" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L433" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M433" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="20">
+        <v>45746.28061377315</v>
+      </c>
+      <c r="B434" s="21" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C434" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D434" s="21">
+        <v>2.0202215E7</v>
+      </c>
+      <c r="E434" s="21" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F434" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G434" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H434" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I434" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J434" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K434" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L434" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M434" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="26">
+        <v>45746.35717142361</v>
+      </c>
+      <c r="B435" s="27" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C435" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D435" s="27">
+        <v>2.0241629E7</v>
+      </c>
+      <c r="E435" s="27" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F435" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G435" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="H435" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I435" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J435" s="30">
+        <v>0.374</v>
+      </c>
+      <c r="K435" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L435" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N435" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="20">
+        <v>45746.358856238425</v>
+      </c>
+      <c r="B436" s="21" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C436" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D436" s="21">
+        <v>2.0193716E7</v>
+      </c>
+      <c r="E436" s="21" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F436" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G436" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H436" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I436" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J436" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K436" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L436" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N436" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="26">
+        <v>45746.36590574074</v>
+      </c>
+      <c r="B437" s="27" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C437" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D437" s="27">
+        <v>2.024272E7</v>
+      </c>
+      <c r="E437" s="27" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F437" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G437" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H437" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I437" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J437" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K437" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L437" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N437" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="20">
+        <v>45746.39676628472</v>
+      </c>
+      <c r="B438" s="21" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C438" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D438" s="21">
+        <v>2.0233214E7</v>
+      </c>
+      <c r="E438" s="21" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F438" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G438" s="23">
+        <v>0.25</v>
+      </c>
+      <c r="H438" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="I438" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="J438" s="24">
+        <v>0.374</v>
+      </c>
+      <c r="K438" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L438" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N438" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="26">
+        <v>45746.410921608796</v>
+      </c>
+      <c r="B439" s="27" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C439" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="D439" s="27">
+        <v>2.0241049E7</v>
+      </c>
+      <c r="E439" s="27" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F439" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G439" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H439" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I439" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J439" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K439" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L439" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M439" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="20">
+        <v>45746.41720606481</v>
+      </c>
+      <c r="B440" s="21" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C440" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D440" s="21">
+        <v>2.0243952E7</v>
+      </c>
+      <c r="E440" s="21" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F440" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G440" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H440" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I440" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J440" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K440" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L440" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N440" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="26">
+        <v>45746.45329149306</v>
+      </c>
+      <c r="B441" s="27" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C441" s="27" t="s">
+        <v>403</v>
+      </c>
+      <c r="D441" s="27">
+        <v>2.0213639E7</v>
+      </c>
+      <c r="E441" s="27" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F441" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G441" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H441" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I441" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J441" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K441" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L441" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M441" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="20">
+        <v>45746.45883722222</v>
+      </c>
+      <c r="B442" s="21" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C442" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="D442" s="21">
+        <v>2.0235218E7</v>
+      </c>
+      <c r="E442" s="21" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F442" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G442" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H442" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I442" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J442" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K442" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L442" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N442" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="26">
+        <v>45746.49584055555</v>
+      </c>
+      <c r="B443" s="27" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C443" s="27" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D443" s="27">
+        <v>2.0227161E7</v>
+      </c>
+      <c r="E443" s="27" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F443" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G443" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H443" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I443" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J443" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K443" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L443" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N443" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="20">
+        <v>45746.50899625</v>
+      </c>
+      <c r="B444" s="21" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C444" s="21" t="s">
+        <v>497</v>
+      </c>
+      <c r="D444" s="21">
+        <v>2.0201731E7</v>
+      </c>
+      <c r="E444" s="21" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F444" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G444" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H444" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I444" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J444" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K444" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L444" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N444" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="26">
+        <v>45746.52590853009</v>
+      </c>
+      <c r="B445" s="27" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C445" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D445" s="27">
+        <v>2.0242546E7</v>
+      </c>
+      <c r="E445" s="27" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F445" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G445" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H445" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I445" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J445" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K445" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L445" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N445" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="20">
+        <v>45746.53597641204</v>
+      </c>
+      <c r="B446" s="21" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C446" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D446" s="21">
+        <v>2.0243942E7</v>
+      </c>
+      <c r="E446" s="21" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F446" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G446" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H446" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I446" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J446" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K446" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L446" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N446" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="26">
+        <v>45746.5489706713</v>
+      </c>
+      <c r="B447" s="27" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C447" s="27" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D447" s="27">
+        <v>2.0241006E7</v>
+      </c>
+      <c r="E447" s="27" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F447" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G447" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H447" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I447" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J447" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K447" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L447" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M447" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="20">
+        <v>45746.562432199076</v>
+      </c>
+      <c r="B448" s="21" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C448" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D448" s="21">
+        <v>2.0243407E7</v>
+      </c>
+      <c r="E448" s="21" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F448" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G448" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="H448" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I448" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J448" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K448" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L448" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N448" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="26">
+        <v>45746.580627523144</v>
+      </c>
+      <c r="B449" s="27" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C449" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D449" s="27">
+        <v>2.0242713E7</v>
+      </c>
+      <c r="E449" s="27" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F449" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G449" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H449" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I449" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J449" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K449" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L449" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M449" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="20">
+        <v>45746.58184784722</v>
+      </c>
+      <c r="B450" s="21" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C450" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D450" s="21">
+        <v>2.0243403E7</v>
+      </c>
+      <c r="E450" s="21" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F450" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G450" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H450" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I450" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J450" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K450" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L450" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M450" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="26">
+        <v>45746.5821388426</v>
+      </c>
+      <c r="B451" s="27" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C451" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D451" s="27">
+        <v>2.024255E7</v>
+      </c>
+      <c r="E451" s="27" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F451" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G451" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H451" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I451" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J451" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K451" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L451" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M451" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="20">
+        <v>45746.59074491898</v>
+      </c>
+      <c r="B452" s="21" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C452" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="D452" s="21">
+        <v>2.0212918E7</v>
+      </c>
+      <c r="E452" s="21" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F452" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G452" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H452" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I452" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J452" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K452" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L452" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N452" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="26">
+        <v>45746.608137187504</v>
+      </c>
+      <c r="B453" s="27" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C453" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D453" s="27">
+        <v>2.0223824E7</v>
+      </c>
+      <c r="E453" s="27" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F453" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G453" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H453" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I453" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J453" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K453" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L453" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N453" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="20">
+        <v>45746.60844902778</v>
+      </c>
+      <c r="B454" s="21" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C454" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="D454" s="21">
+        <v>2.021515E7</v>
+      </c>
+      <c r="E454" s="21" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F454" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G454" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H454" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I454" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J454" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K454" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L454" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N454" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="26">
+        <v>45746.61484513889</v>
+      </c>
+      <c r="B455" s="27" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C455" s="27" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D455" s="27">
+        <v>2.0218005E7</v>
+      </c>
+      <c r="E455" s="27" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F455" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G455" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H455" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I455" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J455" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K455" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L455" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M455" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="20">
+        <v>45746.618841076386</v>
+      </c>
+      <c r="B456" s="21" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C456" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D456" s="21">
+        <v>2.0242716E7</v>
+      </c>
+      <c r="E456" s="21" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F456" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G456" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H456" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I456" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J456" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K456" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L456" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N456" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="26">
+        <v>45746.62319799769</v>
+      </c>
+      <c r="B457" s="27" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C457" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D457" s="27">
+        <v>2.0242203E7</v>
+      </c>
+      <c r="E457" s="27" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F457" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G457" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H457" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I457" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J457" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K457" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L457" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M457" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="20">
+        <v>45746.62967385417</v>
+      </c>
+      <c r="B458" s="21" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C458" s="21" t="s">
+        <v>665</v>
+      </c>
+      <c r="D458" s="21">
+        <v>2.0241012E7</v>
+      </c>
+      <c r="E458" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="F458" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G458" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H458" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I458" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J458" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K458" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L458" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M458" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="26">
+        <v>45746.63536853009</v>
+      </c>
+      <c r="B459" s="27" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C459" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D459" s="27">
+        <v>2.024102E7</v>
+      </c>
+      <c r="E459" s="27" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F459" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G459" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H459" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I459" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J459" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K459" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L459" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M459" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="20">
+        <v>45746.63784806713</v>
+      </c>
+      <c r="B460" s="21" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C460" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="D460" s="21">
+        <v>2.0212527E7</v>
+      </c>
+      <c r="E460" s="21" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F460" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G460" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H460" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I460" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J460" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K460" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L460" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M460" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="26">
+        <v>45746.63944811343</v>
+      </c>
+      <c r="B461" s="27" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C461" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="D461" s="27">
+        <v>2.0231062E7</v>
+      </c>
+      <c r="E461" s="27" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F461" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G461" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H461" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I461" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J461" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K461" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L461" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N461" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="20">
+        <v>45746.641268402775</v>
+      </c>
+      <c r="B462" s="21" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C462" s="21" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D462" s="21">
+        <v>2.023173E7</v>
+      </c>
+      <c r="E462" s="21" t="s">
+        <v>734</v>
+      </c>
+      <c r="F462" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G462" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H462" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I462" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J462" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K462" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L462" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N462" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="26">
+        <v>45746.64227967593</v>
+      </c>
+      <c r="B463" s="27" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C463" s="27" t="s">
+        <v>380</v>
+      </c>
+      <c r="D463" s="27">
+        <v>2.0255273E7</v>
+      </c>
+      <c r="E463" s="27" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F463" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G463" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H463" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I463" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J463" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K463" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="L463" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M463" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="20">
+        <v>45746.6517785301</v>
+      </c>
+      <c r="B464" s="21" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C464" s="21" t="s">
+        <v>497</v>
+      </c>
+      <c r="D464" s="21">
+        <v>2.0241704E7</v>
+      </c>
+      <c r="E464" s="21" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F464" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G464" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H464" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I464" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J464" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K464" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L464" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M464" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="26">
+        <v>45746.6566290162</v>
+      </c>
+      <c r="B465" s="27" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C465" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D465" s="27">
+        <v>2.0246263E7</v>
+      </c>
+      <c r="E465" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="F465" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G465" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H465" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I465" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J465" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K465" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L465" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M465" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="20">
+        <v>45746.660630451384</v>
+      </c>
+      <c r="B466" s="21" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C466" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D466" s="21">
+        <v>2.0243545E7</v>
+      </c>
+      <c r="E466" s="21" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F466" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G466" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="H466" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I466" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J466" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K466" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L466" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M466" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="26">
+        <v>45746.68027813657</v>
+      </c>
+      <c r="B467" s="27" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C467" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D467" s="27">
+        <v>2.0201603E7</v>
+      </c>
+      <c r="E467" s="27" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F467" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G467" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H467" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I467" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J467" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K467" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L467" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M467" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="20">
+        <v>45746.68156667824</v>
+      </c>
+      <c r="B468" s="21" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C468" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D468" s="21">
+        <v>2.0242944E7</v>
+      </c>
+      <c r="E468" s="21" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F468" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G468" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H468" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I468" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J468" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K468" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L468" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M468" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="26">
+        <v>45746.685315925926</v>
+      </c>
+      <c r="B469" s="27" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C469" s="27" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D469" s="27">
+        <v>2.0226769E7</v>
+      </c>
+      <c r="E469" s="27" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F469" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G469" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H469" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I469" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J469" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K469" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L469" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M469" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="20">
+        <v>45746.68831320602</v>
+      </c>
+      <c r="B470" s="21" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C470" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D470" s="21">
+        <v>2.0253006E7</v>
+      </c>
+      <c r="E470" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="F470" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G470" s="23">
+        <v>0.25</v>
+      </c>
+      <c r="H470" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I470" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J470" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K470" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L470" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M470" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="26">
+        <v>45746.70229888889</v>
+      </c>
+      <c r="B471" s="27" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C471" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D471" s="27">
+        <v>2.0241235E7</v>
+      </c>
+      <c r="E471" s="27" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F471" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G471" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H471" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I471" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J471" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K471" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L471" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N471" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="20">
+        <v>45746.70310416666</v>
+      </c>
+      <c r="B472" s="21" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C472" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D472" s="21">
+        <v>2.0245245E7</v>
+      </c>
+      <c r="E472" s="21" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F472" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G472" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H472" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I472" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J472" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K472" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L472" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N472" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="26">
+        <v>45746.713054884254</v>
+      </c>
+      <c r="B473" s="27" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C473" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="D473" s="27">
+        <v>2.0231101E7</v>
+      </c>
+      <c r="E473" s="27" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F473" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G473" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H473" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I473" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J473" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K473" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L473" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N473" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="20">
+        <v>45746.714470127314</v>
+      </c>
+      <c r="B474" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C474" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D474" s="21">
+        <v>2.0243513E7</v>
+      </c>
+      <c r="E474" s="21" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F474" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G474" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H474" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I474" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J474" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K474" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L474" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N474" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="26">
+        <v>45746.71882628472</v>
+      </c>
+      <c r="B475" s="27" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C475" s="27" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D475" s="27">
+        <v>2.024106E7</v>
+      </c>
+      <c r="E475" s="27" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F475" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G475" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H475" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I475" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J475" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K475" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L475" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N475" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="20">
+        <v>45746.72464746528</v>
+      </c>
+      <c r="B476" s="21" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C476" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D476" s="21">
+        <v>2.0243713E7</v>
+      </c>
+      <c r="E476" s="21" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F476" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G476" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H476" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I476" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J476" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K476" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L476" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N476" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="26">
+        <v>45746.729652152775</v>
+      </c>
+      <c r="B477" s="27" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C477" s="27" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D477" s="27">
+        <v>2.0245268E7</v>
+      </c>
+      <c r="E477" s="27" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F477" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G477" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H477" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I477" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J477" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K477" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L477" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M477" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="20">
+        <v>45746.73242351852</v>
+      </c>
+      <c r="B478" s="21" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C478" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D478" s="21">
+        <v>2.0231039E7</v>
+      </c>
+      <c r="E478" s="21" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F478" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G478" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H478" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I478" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J478" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K478" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L478" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N478" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="26">
+        <v>45746.739283229166</v>
+      </c>
+      <c r="B479" s="27" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C479" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="D479" s="27">
+        <v>2.0246627E7</v>
+      </c>
+      <c r="E479" s="27" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F479" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G479" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H479" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I479" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J479" s="30">
+        <v>0.002</v>
+      </c>
+      <c r="K479" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L479" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M479" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="20">
+        <v>45746.752131099536</v>
+      </c>
+      <c r="B480" s="21" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C480" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D480" s="21">
+        <v>2.0242622E7</v>
+      </c>
+      <c r="E480" s="21" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F480" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G480" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H480" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I480" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J480" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K480" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L480" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N480" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="26">
+        <v>45746.7531329051</v>
+      </c>
+      <c r="B481" s="27" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C481" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="D481" s="27">
+        <v>2.0243515E7</v>
+      </c>
+      <c r="E481" s="27" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F481" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G481" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H481" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I481" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J481" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K481" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L481" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M481" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="20">
+        <v>45746.75386311342</v>
+      </c>
+      <c r="B482" s="21" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C482" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D482" s="21">
+        <v>2.0242717E7</v>
+      </c>
+      <c r="E482" s="21" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F482" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G482" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H482" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I482" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J482" s="24">
+        <v>0.374</v>
+      </c>
+      <c r="K482" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L482" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M482" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="26">
+        <v>45746.75394715278</v>
+      </c>
+      <c r="B483" s="27" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C483" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D483" s="27">
+        <v>2.0243023E7</v>
+      </c>
+      <c r="E483" s="27" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F483" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G483" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H483" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I483" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J483" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K483" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="L483" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M483" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="20">
+        <v>45746.75471231481</v>
+      </c>
+      <c r="B484" s="21" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C484" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D484" s="21">
+        <v>2.0243729E7</v>
+      </c>
+      <c r="E484" s="21" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F484" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G484" s="23">
+        <v>0.25</v>
+      </c>
+      <c r="H484" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I484" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J484" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K484" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L484" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N484" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="26">
+        <v>45746.75864418982</v>
+      </c>
+      <c r="B485" s="27" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C485" s="27" t="s">
+        <v>497</v>
+      </c>
+      <c r="D485" s="27">
+        <v>2.0231725E7</v>
+      </c>
+      <c r="E485" s="27" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F485" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G485" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H485" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I485" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J485" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K485" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="L485" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M485" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="20">
+        <v>45746.758687511574</v>
+      </c>
+      <c r="B486" s="21" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C486" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D486" s="21">
+        <v>2.0226628E7</v>
+      </c>
+      <c r="E486" s="21" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F486" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G486" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H486" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I486" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J486" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K486" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L486" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M486" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="26">
+        <v>45746.76017674769</v>
+      </c>
+      <c r="B487" s="27" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C487" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D487" s="27">
+        <v>2.0243042E7</v>
+      </c>
+      <c r="E487" s="27" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F487" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G487" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H487" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I487" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J487" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K487" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L487" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N487" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="20">
+        <v>45746.765288124996</v>
+      </c>
+      <c r="B488" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C488" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D488" s="21">
+        <v>2.0242315E7</v>
+      </c>
+      <c r="E488" s="21" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F488" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G488" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H488" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I488" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J488" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K488" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L488" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M488" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="26">
+        <v>45746.76763315972</v>
+      </c>
+      <c r="B489" s="27" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C489" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D489" s="27">
+        <v>2.0227056E7</v>
+      </c>
+      <c r="E489" s="27" t="s">
+        <v>982</v>
+      </c>
+      <c r="F489" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G489" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H489" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I489" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J489" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K489" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L489" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N489" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="20">
+        <v>45746.78212319444</v>
+      </c>
+      <c r="B490" s="21" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C490" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D490" s="21">
+        <v>2.0227057E7</v>
+      </c>
+      <c r="E490" s="21" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F490" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G490" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H490" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I490" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J490" s="24">
+        <v>0.374</v>
+      </c>
+      <c r="K490" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L490" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N490" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="26">
+        <v>45746.787000219905</v>
+      </c>
+      <c r="B491" s="27" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C491" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D491" s="27">
+        <v>2.0243818E7</v>
+      </c>
+      <c r="E491" s="27" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F491" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G491" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H491" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I491" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J491" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K491" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L491" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N491" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="20">
+        <v>45746.78860883102</v>
+      </c>
+      <c r="B492" s="21" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C492" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D492" s="21">
+        <v>2.0222999E7</v>
+      </c>
+      <c r="E492" s="21" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F492" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G492" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H492" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I492" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J492" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K492" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L492" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N492" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="26">
+        <v>45746.79436172453</v>
+      </c>
+      <c r="B493" s="27" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C493" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="D493" s="27">
+        <v>2.0215255E7</v>
+      </c>
+      <c r="E493" s="27" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F493" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G493" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H493" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I493" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J493" s="30">
+        <v>0.002</v>
+      </c>
+      <c r="K493" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L493" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N493" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="20">
+        <v>45746.798601331015</v>
+      </c>
+      <c r="B494" s="21" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C494" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="D494" s="21">
+        <v>2.0215152E7</v>
+      </c>
+      <c r="E494" s="21" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F494" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G494" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H494" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I494" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J494" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K494" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L494" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N494" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="26">
+        <v>45746.80023663194</v>
+      </c>
+      <c r="B495" s="27" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C495" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D495" s="27">
+        <v>2.0246236E7</v>
+      </c>
+      <c r="E495" s="27" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F495" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G495" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H495" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I495" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J495" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K495" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L495" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M495" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="20">
+        <v>45746.80070815972</v>
+      </c>
+      <c r="B496" s="21" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C496" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D496" s="21">
+        <v>2.0211537E7</v>
+      </c>
+      <c r="E496" s="21" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F496" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G496" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="H496" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I496" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J496" s="24">
+        <v>0.002</v>
+      </c>
+      <c r="K496" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L496" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M496" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="26">
+        <v>45746.8043307176</v>
+      </c>
+      <c r="B497" s="27" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C497" s="27" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D497" s="27">
+        <v>2.025394E7</v>
+      </c>
+      <c r="E497" s="27" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F497" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G497" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H497" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I497" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J497" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K497" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L497" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N497" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="20">
+        <v>45746.80473570601</v>
+      </c>
+      <c r="B498" s="21" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C498" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D498" s="21">
+        <v>2.0223517E7</v>
+      </c>
+      <c r="E498" s="21" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F498" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G498" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H498" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I498" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J498" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K498" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L498" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M498" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="26">
+        <v>45746.80908643518</v>
+      </c>
+      <c r="B499" s="27" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C499" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D499" s="27">
+        <v>2.0243012E7</v>
+      </c>
+      <c r="E499" s="27" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F499" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G499" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H499" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I499" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J499" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K499" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L499" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M499" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="20">
+        <v>45746.81080715278</v>
+      </c>
+      <c r="B500" s="21" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C500" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D500" s="21">
+        <v>2.0224116E7</v>
+      </c>
+      <c r="E500" s="21" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F500" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G500" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H500" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I500" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J500" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K500" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L500" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N500" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="26">
+        <v>45746.81316464121</v>
+      </c>
+      <c r="B501" s="27" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C501" s="27" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D501" s="27">
+        <v>2.0215202E7</v>
+      </c>
+      <c r="E501" s="27" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F501" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G501" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H501" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I501" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J501" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K501" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L501" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M501" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="20">
+        <v>45746.81685120371</v>
+      </c>
+      <c r="B502" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C502" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D502" s="21">
+        <v>2.0233433E7</v>
+      </c>
+      <c r="E502" s="21" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F502" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G502" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H502" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I502" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J502" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K502" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L502" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M502" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="26">
+        <v>45746.81764559028</v>
+      </c>
+      <c r="B503" s="27" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C503" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D503" s="27">
+        <v>2.0254146E7</v>
+      </c>
+      <c r="E503" s="27" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F503" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G503" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H503" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I503" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J503" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K503" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L503" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M503" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="20">
+        <v>45746.81771408565</v>
+      </c>
+      <c r="B504" s="21" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C504" s="21" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D504" s="21">
+        <v>2.0212503E7</v>
+      </c>
+      <c r="E504" s="21" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F504" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G504" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H504" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I504" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J504" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K504" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L504" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N504" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="26">
+        <v>45746.81977003472</v>
+      </c>
+      <c r="B505" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C505" s="27" t="s">
+        <v>460</v>
+      </c>
+      <c r="D505" s="27">
+        <v>2.0215238E7</v>
+      </c>
+      <c r="E505" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F505" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G505" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H505" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I505" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J505" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K505" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L505" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N505" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="20">
+        <v>45746.82178457176</v>
+      </c>
+      <c r="B506" s="21" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C506" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D506" s="21">
+        <v>2.020412E7</v>
+      </c>
+      <c r="E506" s="21" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F506" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G506" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="H506" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I506" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J506" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K506" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L506" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N506" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="26">
+        <v>45746.82299260417</v>
+      </c>
+      <c r="B507" s="27" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C507" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D507" s="27">
+        <v>2.0243035E7</v>
+      </c>
+      <c r="E507" s="27" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F507" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G507" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H507" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I507" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J507" s="30">
+        <v>0.374</v>
+      </c>
+      <c r="K507" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L507" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N507" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="20">
+        <v>45746.82544659722</v>
+      </c>
+      <c r="B508" s="21" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C508" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D508" s="21">
+        <v>2.0227107E7</v>
+      </c>
+      <c r="E508" s="21" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F508" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G508" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H508" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I508" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J508" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K508" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L508" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M508" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="26">
+        <v>45746.82811623842</v>
+      </c>
+      <c r="B509" s="27" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C509" s="27" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D509" s="27">
+        <v>2.020162E7</v>
+      </c>
+      <c r="E509" s="27" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F509" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G509" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H509" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I509" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J509" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K509" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L509" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M509" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="20">
+        <v>45746.82879918981</v>
+      </c>
+      <c r="B510" s="21" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C510" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D510" s="21">
+        <v>2.0242949E7</v>
+      </c>
+      <c r="E510" s="21" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F510" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G510" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H510" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I510" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J510" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K510" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L510" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M510" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="26">
+        <v>45746.829848946756</v>
+      </c>
+      <c r="B511" s="27" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C511" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="D511" s="27">
+        <v>2.024342E7</v>
+      </c>
+      <c r="E511" s="27" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F511" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G511" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H511" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I511" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J511" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K511" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L511" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N511" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="20">
+        <v>45746.83418644676</v>
+      </c>
+      <c r="B512" s="21" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C512" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D512" s="21">
+        <v>2.0252433E7</v>
+      </c>
+      <c r="E512" s="21" t="s">
+        <v>787</v>
+      </c>
+      <c r="F512" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G512" s="23">
+        <v>0.25</v>
+      </c>
+      <c r="H512" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I512" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J512" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K512" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L512" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M512" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="26">
+        <v>45746.83446896991</v>
+      </c>
+      <c r="B513" s="27" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C513" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D513" s="27">
+        <v>2.0193262E7</v>
+      </c>
+      <c r="E513" s="27" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F513" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G513" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H513" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I513" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J513" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K513" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L513" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M513" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="20">
+        <v>45746.83688152778</v>
+      </c>
+      <c r="B514" s="21" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C514" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D514" s="21">
+        <v>2.0195174E7</v>
+      </c>
+      <c r="E514" s="21" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F514" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G514" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H514" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I514" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J514" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K514" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L514" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M514" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="26">
+        <v>45746.84829753472</v>
+      </c>
+      <c r="B515" s="27" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C515" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="D515" s="27">
+        <v>2.0223529E7</v>
+      </c>
+      <c r="E515" s="27" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F515" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G515" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H515" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I515" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J515" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K515" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L515" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M515" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="20">
+        <v>45746.84855282407</v>
+      </c>
+      <c r="B516" s="21" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C516" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D516" s="21">
+        <v>2.0242838E7</v>
+      </c>
+      <c r="E516" s="21" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F516" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G516" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H516" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I516" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J516" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K516" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L516" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M516" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="26">
+        <v>45746.84989359954</v>
+      </c>
+      <c r="B517" s="27" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C517" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D517" s="27">
+        <v>2.020161E7</v>
+      </c>
+      <c r="E517" s="27" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F517" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G517" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H517" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I517" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J517" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K517" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L517" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M517" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="20">
+        <v>45746.852740648144</v>
+      </c>
+      <c r="B518" s="21" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C518" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="D518" s="21">
+        <v>2.0243303E7</v>
+      </c>
+      <c r="E518" s="21" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F518" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G518" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H518" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I518" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J518" s="24">
+        <v>0.374</v>
+      </c>
+      <c r="K518" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L518" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N518" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="26">
+        <v>45746.85437243056</v>
+      </c>
+      <c r="B519" s="27" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C519" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D519" s="27">
+        <v>2.0222326E7</v>
+      </c>
+      <c r="E519" s="27" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F519" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G519" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H519" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I519" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J519" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K519" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="L519" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N519" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="20">
+        <v>45746.86002396991</v>
+      </c>
+      <c r="B520" s="21" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C520" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D520" s="21">
+        <v>2.0241611E7</v>
+      </c>
+      <c r="E520" s="21" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F520" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G520" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H520" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I520" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J520" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K520" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L520" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N520" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="26">
+        <v>45746.863420127316</v>
+      </c>
+      <c r="B521" s="27" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C521" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D521" s="27">
+        <v>2.0241229E7</v>
+      </c>
+      <c r="E521" s="27" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F521" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G521" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H521" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I521" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J521" s="30">
+        <v>0.374</v>
+      </c>
+      <c r="K521" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L521" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M521" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="20">
+        <v>45746.8674712037</v>
+      </c>
+      <c r="B522" s="21" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C522" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D522" s="21">
+        <v>2.0242537E7</v>
+      </c>
+      <c r="E522" s="21" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F522" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G522" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H522" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I522" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J522" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K522" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L522" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M522" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="26">
+        <v>45746.869162233794</v>
+      </c>
+      <c r="B523" s="27" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C523" s="27" t="s">
+        <v>380</v>
+      </c>
+      <c r="D523" s="27">
+        <v>2.0245223E7</v>
+      </c>
+      <c r="E523" s="27" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F523" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G523" s="29">
+        <v>0.25</v>
+      </c>
+      <c r="H523" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I523" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J523" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K523" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L523" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M523" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="20">
+        <v>45746.86945090278</v>
+      </c>
+      <c r="B524" s="21" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C524" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D524" s="21">
+        <v>2.0203056E7</v>
+      </c>
+      <c r="E524" s="21" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F524" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G524" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H524" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I524" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J524" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K524" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L524" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M524" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="26">
+        <v>45746.869621261576</v>
+      </c>
+      <c r="B525" s="27" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C525" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D525" s="27">
+        <v>2.0242214E7</v>
+      </c>
+      <c r="E525" s="27" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F525" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G525" s="29">
+        <v>0.25</v>
+      </c>
+      <c r="H525" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I525" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="J525" s="30">
+        <v>0.374</v>
+      </c>
+      <c r="K525" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L525" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M525" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="20">
+        <v>45746.877889166666</v>
+      </c>
+      <c r="B526" s="21" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C526" s="21" t="s">
+        <v>604</v>
+      </c>
+      <c r="D526" s="21">
+        <v>2.0231212E7</v>
+      </c>
+      <c r="E526" s="21" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F526" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G526" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H526" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I526" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J526" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K526" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L526" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N526" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="26">
+        <v>45746.879173124995</v>
+      </c>
+      <c r="B527" s="27" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C527" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D527" s="27">
+        <v>2.0203021E7</v>
+      </c>
+      <c r="E527" s="27" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F527" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G527" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H527" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I527" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J527" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K527" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L527" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N527" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="20">
+        <v>45746.88099289352</v>
+      </c>
+      <c r="B528" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C528" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="D528" s="21">
+        <v>2.0243633E7</v>
+      </c>
+      <c r="E528" s="21" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F528" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G528" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H528" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I528" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J528" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K528" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L528" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N528" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="26">
+        <v>45746.88134274306</v>
+      </c>
+      <c r="B529" s="27" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C529" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D529" s="27">
+        <v>2.0246918E7</v>
+      </c>
+      <c r="E529" s="27" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F529" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G529" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H529" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I529" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J529" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K529" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L529" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N529" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="20">
+        <v>45746.88160434028</v>
+      </c>
+      <c r="B530" s="21" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C530" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D530" s="21">
+        <v>2.0217124E7</v>
+      </c>
+      <c r="E530" s="21" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F530" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G530" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H530" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I530" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J530" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K530" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L530" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M530" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="26">
+        <v>45746.88161493056</v>
+      </c>
+      <c r="B531" s="27" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C531" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="D531" s="27">
+        <v>2.0205117E7</v>
+      </c>
+      <c r="E531" s="27" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F531" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G531" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H531" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I531" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J531" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K531" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L531" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M531" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="20">
+        <v>45746.882780127315</v>
+      </c>
+      <c r="B532" s="21" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C532" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D532" s="21">
+        <v>2.0242969E7</v>
+      </c>
+      <c r="E532" s="21" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F532" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G532" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H532" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I532" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J532" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K532" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L532" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M532" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="26">
+        <v>45746.88302202546</v>
+      </c>
+      <c r="B533" s="27" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C533" s="27" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D533" s="27">
+        <v>2.0243533E7</v>
+      </c>
+      <c r="E533" s="27" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F533" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G533" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H533" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I533" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J533" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K533" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L533" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N533" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="20">
+        <v>45746.88387844907</v>
+      </c>
+      <c r="B534" s="21" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C534" s="21" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D534" s="21">
+        <v>2.0183016E7</v>
+      </c>
+      <c r="E534" s="21" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F534" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G534" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H534" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I534" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J534" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K534" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L534" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N534" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="26">
+        <v>45746.88481732639</v>
+      </c>
+      <c r="B535" s="27" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C535" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="D535" s="27">
+        <v>2.0246626E7</v>
+      </c>
+      <c r="E535" s="27" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F535" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G535" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H535" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I535" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J535" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K535" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L535" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N535" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="20">
+        <v>45746.88495798611</v>
+      </c>
+      <c r="B536" s="21" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C536" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D536" s="21">
+        <v>2.0202362E7</v>
+      </c>
+      <c r="E536" s="21" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F536" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G536" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H536" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I536" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J536" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K536" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="L536" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M536" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="26">
+        <v>45746.886641793986</v>
+      </c>
+      <c r="B537" s="27" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C537" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D537" s="27">
+        <v>2.0206612E7</v>
+      </c>
+      <c r="E537" s="27" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F537" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G537" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H537" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I537" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J537" s="30">
+        <v>0.374</v>
+      </c>
+      <c r="K537" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L537" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N537" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="20">
+        <v>45746.88740869213</v>
+      </c>
+      <c r="B538" s="21" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C538" s="21" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D538" s="21">
+        <v>2.0221108E7</v>
+      </c>
+      <c r="E538" s="21" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F538" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G538" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H538" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I538" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J538" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K538" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="L538" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M538" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="26">
+        <v>45746.88752438658</v>
+      </c>
+      <c r="B539" s="27" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C539" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D539" s="27">
+        <v>2.0223232E7</v>
+      </c>
+      <c r="E539" s="27" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F539" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G539" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="H539" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I539" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J539" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K539" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L539" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M539" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="20">
+        <v>45746.890109155094</v>
+      </c>
+      <c r="B540" s="21" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C540" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D540" s="21">
+        <v>2.0202927E7</v>
+      </c>
+      <c r="E540" s="21" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F540" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G540" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H540" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I540" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J540" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K540" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L540" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N540" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="26">
+        <v>45746.89100025463</v>
+      </c>
+      <c r="B541" s="27" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C541" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="D541" s="27">
+        <v>2.024109E7</v>
+      </c>
+      <c r="E541" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="F541" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G541" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H541" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I541" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J541" s="30">
+        <v>0.374</v>
+      </c>
+      <c r="K541" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L541" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N541" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="20">
+        <v>45746.89396555556</v>
+      </c>
+      <c r="B542" s="21" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C542" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D542" s="21">
+        <v>2.0242566E7</v>
+      </c>
+      <c r="E542" s="21" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F542" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G542" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H542" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I542" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J542" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K542" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L542" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M542" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="26">
+        <v>45746.89671376157</v>
+      </c>
+      <c r="B543" s="27" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C543" s="27" t="s">
+        <v>957</v>
+      </c>
+      <c r="D543" s="27">
+        <v>2043817.0</v>
+      </c>
+      <c r="E543" s="27" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F543" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G543" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H543" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I543" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J543" s="30">
+        <v>0.151</v>
+      </c>
+      <c r="K543" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="L543" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N543" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="20">
+        <v>45746.90105075232</v>
+      </c>
+      <c r="B544" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C544" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D544" s="21">
+        <v>2.0212763E7</v>
+      </c>
+      <c r="E544" s="21" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F544" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G544" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H544" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I544" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J544" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K544" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L544" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N544" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="26">
+        <v>45746.90464581018</v>
+      </c>
+      <c r="B545" s="27" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C545" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="D545" s="27">
+        <v>2.0343429E7</v>
+      </c>
+      <c r="E545" s="27" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F545" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G545" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H545" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I545" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J545" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K545" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L545" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N545" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="20">
+        <v>45746.90565821759</v>
+      </c>
+      <c r="B546" s="21" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C546" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D546" s="21">
+        <v>2.0212105E7</v>
+      </c>
+      <c r="E546" s="21" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F546" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G546" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H546" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I546" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J546" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K546" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L546" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M546" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="26">
+        <v>45746.90774230324</v>
+      </c>
+      <c r="B547" s="27" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C547" s="27" t="s">
+        <v>403</v>
+      </c>
+      <c r="D547" s="27">
+        <v>2.0243604E7</v>
+      </c>
+      <c r="E547" s="27" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F547" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G547" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H547" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I547" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="J547" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K547" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L547" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M547" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="20">
+        <v>45746.908202499995</v>
+      </c>
+      <c r="B548" s="21" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C548" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D548" s="21">
+        <v>2.0236228E7</v>
+      </c>
+      <c r="E548" s="21" t="s">
+        <v>1237</v>
+      </c>
+      <c r="F548" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G548" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H548" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I548" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J548" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K548" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L548" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M548" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="26">
+        <v>45746.90824510416</v>
+      </c>
+      <c r="B549" s="27" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C549" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="D549" s="27">
+        <v>2.0241105E7</v>
+      </c>
+      <c r="E549" s="27" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F549" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G549" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H549" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I549" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J549" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K549" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L549" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N549" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="20">
+        <v>45746.91048133102</v>
+      </c>
+      <c r="B550" s="21" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C550" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D550" s="21">
+        <v>2.0253725E7</v>
+      </c>
+      <c r="E550" s="21" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F550" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G550" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H550" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I550" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J550" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K550" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L550" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M550" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="26">
+        <v>45746.91110815972</v>
+      </c>
+      <c r="B551" s="27" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C551" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D551" s="27">
+        <v>2.0232128E7</v>
+      </c>
+      <c r="E551" s="27" t="s">
+        <v>876</v>
+      </c>
+      <c r="F551" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G551" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H551" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I551" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J551" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K551" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L551" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N551" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="20">
+        <v>45746.91122233796</v>
+      </c>
+      <c r="B552" s="21" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C552" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D552" s="21">
+        <v>2.0231618E7</v>
+      </c>
+      <c r="E552" s="21" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F552" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G552" s="23">
+        <v>0.25</v>
+      </c>
+      <c r="H552" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I552" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J552" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K552" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L552" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M552" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="26">
+        <v>45746.9123740625</v>
+      </c>
+      <c r="B553" s="27" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C553" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D553" s="27">
+        <v>2.0212997E7</v>
+      </c>
+      <c r="E553" s="27" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F553" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G553" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="H553" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I553" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J553" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K553" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L553" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N553" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="20">
+        <v>45746.91258355324</v>
+      </c>
+      <c r="B554" s="21" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C554" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D554" s="21">
+        <v>2.0203048E7</v>
+      </c>
+      <c r="E554" s="21" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F554" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G554" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="H554" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="I554" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J554" s="24">
+        <v>0.151</v>
+      </c>
+      <c r="K554" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L554" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N554" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="26">
+        <v>45746.913721770834</v>
+      </c>
+      <c r="B555" s="27" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C555" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D555" s="27">
+        <v>2.0243841E7</v>
+      </c>
+      <c r="E555" s="27" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F555" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G555" s="29">
+        <v>0.25</v>
+      </c>
+      <c r="H555" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I555" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J555" s="30">
+        <v>0.059</v>
+      </c>
+      <c r="K555" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L555" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M555" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="20">
+        <v>45746.91416850695</v>
+      </c>
+      <c r="B556" s="21" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C556" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D556" s="21">
+        <v>2.0223063E7</v>
+      </c>
+      <c r="E556" s="21" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F556" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G556" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="H556" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I556" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J556" s="24">
+        <v>0.059</v>
+      </c>
+      <c r="K556" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L556" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N556" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="32">
+        <v>45746.91730565972</v>
+      </c>
+      <c r="B557" s="33" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C557" s="33" t="s">
+        <v>342</v>
+      </c>
+      <c r="D557" s="33">
+        <v>2.0215177E7</v>
+      </c>
+      <c r="E557" s="33" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F557" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="G557" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="H557" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I557" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J557" s="36">
+        <v>0.059</v>
+      </c>
+      <c r="K557" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="L557" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="M557" s="33" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
